--- a/data/monthly/【2025年12月】月次数値.xlsx
+++ b/data/monthly/【2025年12月】月次数値.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="240">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -382,13 +382,487 @@
   </si>
   <si>
     <t>Beauty Salon Arona</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【せがわ歯科クリニック】です🦷✨...</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【ORINAS】です🍽️✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【CasualClub青】です🎤✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Mix Bar Blo】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【はんすう】です🍦✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍴肴家 信清🍷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 家系ラーメン武将家　浅草店
+10月5日にオープンした『家系らーめん...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️【特別な日のご褒美に】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 和牛焼肉としお
+🥩和牛焼肉の新境地へ— 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍜日々“育てる”一杯、ここにあり🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷✨クオリティ高×価格安×lowkeyな接客✨🍴...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼2〜3歳のお子さまも大歓迎👶✨／...</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>Instagram投稿: インプラント治療なら「上志津中央歯科」🌟...</t>
+  </si>
+  <si>
+    <t>recently_completed</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 中洲にあるミュージックカラオケバー！Food持ち込み可🍴🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥【香り豊かな炭火焼と多彩な日本酒が楽しめる！】🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: んにちは！【Mont Blanc】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟SUNRISEガールズバー｜豊田市山之手🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 株式会社 TechVoice・FRETTA 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📢 株式会社 TechVoice・FRETTA スタッフ募集中！ 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🏡☕canurip Cafe☕🏡
+茨木に佇む韓国風古民家カフェღ...</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻 鉄板居酒屋こぐま 🔥
+🏡 アットホームな空間で、心もお腹も大満足！...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 至福のひとときを、すすきの 蟹一 で。
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶 合同会社 大和・北海道の幸とお酒 たかふじ 🐟
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨ 天ぷら むらやま｜吉祥寺 ✨
+ゆったりとした カウンター席...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 遠心太助 – 新発想の洗浄ツールで塗装コスト削減！ 🌍
+🔹...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 pikku onni 🍽️
+🐟 北海道の海の恵み ×...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉処 縁結び｜鮮度抜群の極上焼肉 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤 カラオケサーカス 調布店 🎪✨
+東京・調布市の音楽オアシス！🌆🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟大林歯科医院｜千葉県美浜区幕張西🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟栄駅から徒歩2分の歯医者【日生歯科診療所】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟府中市の歯医者【たかすぎ歯科クリニック】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟かわらもと歯科｜大阪市・吹田市🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻【リーズナブルにたくさん食べたいなら「居酒屋一（ichi）」】🍻...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【国分町に新しい刺激を！】✨
+「Extreme Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌻季節の食材を使った心温まるお料理とお酒🌻...</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟【焼鳥の真髄、ここにあり】🌟
+「焼鳥酒場...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌙【川越の夜をおしゃれに楽しむならここ！】🌙
+「AMUSEMENT Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🐾✨ Heart Dog ✨🐶
+ドッグカフェ 庵（いおり） OPEN！...</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️【リラックスしたひとときを「HIDEOUT」で】🍷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥 ホルモン 焼肉 楽丸...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩✨ステーキTaka✨🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥 炭火焼とり 隼...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 えびすバル –自家製ローストビーフと自然派ワインのマリアージュを🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨ 高岡市のバー【NUTS】へようこそ！🍹...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️ おるたなキッチン – カフェみたいな定食屋で心ほっこりごはん時間☕🍱...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: LEAP SPORTS GYMで、一緒に成長しよう！💪🔥
+🏋️‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌴 Manly Australian Cafe ＆ Bar 🇦🇺
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦌🦪 鹿肉＆オイスターバル SLOW...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤✨ snack &amp; karaoke bar Belle 🍸🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶✨ 居酒屋1484（イシバシ） 🍽️🎣
+📍 大宮駅東口から徒歩すぐ！
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍁 旬彩和食よし田 🍁
+📍 つくば市の本格和食店
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌿 HATASU 🌱
+植物と暮らそう。
+何気ない日常に 緑...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 肉とワインのイタリアン酒場 more 前橋店 🥩
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 肉とワインのイタリアン酒場 more 高崎店 🥩
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥢 中華バル Chiry - チャイリー 🍻
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎉【スナックバー Reina 求人募集】🎉...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 東高円寺店 🍽...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 新高円寺店 🍽...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥢【とんかつ樹｜こだわり抜いた食材と空間で味わう極上のひととき】🥢...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 経堂店 🔥
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 炭火焼肉 からし亭 八戸店 🥢
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 三沢店 🍚✨
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】🥋✨...</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟 2024年9月、津田沼にNEW OPEN！🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【地域密着！いつでも安心のかかりつけ歯科】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【日野市で予防歯科なら！】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【透明感のある白い歯を目指して】✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎵✨ BAR EIT8で特別なひと時を✨🎵...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【求人募集】✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【船橋市で理想の口元へ】🦷
+医療法人社団哲の子会...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶居酒屋ちるとSake 三軒茶屋店✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷✨ チロル歯科 ✨🦷...</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️✨...</t>
+  </si>
+  <si>
+    <t>2026-12-28</t>
+  </si>
+  <si>
+    <t>Instagram投稿: "洋食ビストロコパンへようこそ！ハンバーグが自慢の喫茶店です🍔✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: "🍸 ＆ジン 🍸
+バーテンダー監修のカジュアルなジン酒場✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: もちもちの魔法で心もお腹も満たす✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨arphills✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【韓国酒場 チィヘッソ】🇰🇷🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌍スパイス香る夜の冒険へ🍷
+【muy bien｜ムイビエン】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼ドキドキ💓はじめてのスポーツ体験！／...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】新しい仲間を募集しています！🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【鮨一花】🍣✨
+豊水すすきの駅から徒歩1分🚶‍♂️🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「SEA DROP Roast...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨2024年9月20日 NEW OPEN✨
+Hairsalon...</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>初回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Instagram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>投稿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">: 🦷 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>海岸歯科室｜インビザライン矯正
+「見えない矯正で、理想の笑顔へ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>✨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ショカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -403,6 +877,19 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -428,9 +915,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -732,7 +1222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y57"/>
+  <dimension ref="A1:Y166"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -4738,6 +5228,7664 @@
       </c>
       <c r="Y57">
         <v>41.534883999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58">
+        <v>116</v>
+      </c>
+      <c r="G58" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58">
+        <v>4616</v>
+      </c>
+      <c r="I58">
+        <v>1.549393</v>
+      </c>
+      <c r="J58">
+        <v>42.474137929999998</v>
+      </c>
+      <c r="K58">
+        <v>160</v>
+      </c>
+      <c r="L58" t="s">
+        <v>30</v>
+      </c>
+      <c r="M58">
+        <v>4927</v>
+      </c>
+      <c r="N58" t="s">
+        <v>122</v>
+      </c>
+      <c r="O58">
+        <v>7152</v>
+      </c>
+      <c r="P58">
+        <v>688.89820999999995</v>
+      </c>
+      <c r="Q58">
+        <v>116</v>
+      </c>
+      <c r="S58">
+        <v>42.474138000000004</v>
+      </c>
+      <c r="T58">
+        <v>1.6219239999999999</v>
+      </c>
+      <c r="U58">
+        <v>192</v>
+      </c>
+      <c r="V58">
+        <v>2.684564</v>
+      </c>
+      <c r="W58">
+        <v>25.661458</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" t="s">
+        <v>81</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59">
+        <v>2627</v>
+      </c>
+      <c r="I59">
+        <v>1.483061</v>
+      </c>
+      <c r="J59">
+        <v>61.537500000000001</v>
+      </c>
+      <c r="K59">
+        <v>160</v>
+      </c>
+      <c r="L59" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59">
+        <v>4923</v>
+      </c>
+      <c r="N59" t="s">
+        <v>124</v>
+      </c>
+      <c r="O59">
+        <v>3896</v>
+      </c>
+      <c r="P59">
+        <v>1263.6036959999999</v>
+      </c>
+      <c r="Q59">
+        <v>80</v>
+      </c>
+      <c r="S59">
+        <v>61.537500000000001</v>
+      </c>
+      <c r="T59">
+        <v>2.053388</v>
+      </c>
+      <c r="U59">
+        <v>102</v>
+      </c>
+      <c r="V59">
+        <v>2.6180699999999999</v>
+      </c>
+      <c r="W59">
+        <v>48.264705999999997</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60">
+        <v>176</v>
+      </c>
+      <c r="G60" t="s">
+        <v>39</v>
+      </c>
+      <c r="H60">
+        <v>4180</v>
+      </c>
+      <c r="I60">
+        <v>1.5100480000000001</v>
+      </c>
+      <c r="J60">
+        <v>27.988636360000001</v>
+      </c>
+      <c r="K60">
+        <v>160</v>
+      </c>
+      <c r="L60" t="s">
+        <v>30</v>
+      </c>
+      <c r="M60">
+        <v>4926</v>
+      </c>
+      <c r="N60" t="s">
+        <v>126</v>
+      </c>
+      <c r="O60">
+        <v>6312</v>
+      </c>
+      <c r="P60">
+        <v>780.41825100000005</v>
+      </c>
+      <c r="Q60">
+        <v>176</v>
+      </c>
+      <c r="S60">
+        <v>27.988636</v>
+      </c>
+      <c r="T60">
+        <v>2.7883399999999998</v>
+      </c>
+      <c r="U60">
+        <v>249</v>
+      </c>
+      <c r="V60">
+        <v>3.9448669999999999</v>
+      </c>
+      <c r="W60">
+        <v>19.783132999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>127</v>
+      </c>
+      <c r="D61" t="s">
+        <v>81</v>
+      </c>
+      <c r="E61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61" t="s">
+        <v>39</v>
+      </c>
+      <c r="H61">
+        <v>1721</v>
+      </c>
+      <c r="I61">
+        <v>1.23068</v>
+      </c>
+      <c r="J61">
+        <v>86.224137929999998</v>
+      </c>
+      <c r="K61">
+        <v>160</v>
+      </c>
+      <c r="L61" t="s">
+        <v>30</v>
+      </c>
+      <c r="M61">
+        <v>5001</v>
+      </c>
+      <c r="N61" t="s">
+        <v>126</v>
+      </c>
+      <c r="O61">
+        <v>2118</v>
+      </c>
+      <c r="P61">
+        <v>2361.1898019999999</v>
+      </c>
+      <c r="Q61">
+        <v>58</v>
+      </c>
+      <c r="S61">
+        <v>86.224137999999996</v>
+      </c>
+      <c r="T61">
+        <v>2.738432</v>
+      </c>
+      <c r="U61">
+        <v>66</v>
+      </c>
+      <c r="V61">
+        <v>3.1161469999999998</v>
+      </c>
+      <c r="W61">
+        <v>75.772727000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62">
+        <v>218</v>
+      </c>
+      <c r="G62" t="s">
+        <v>39</v>
+      </c>
+      <c r="H62">
+        <v>3510</v>
+      </c>
+      <c r="I62">
+        <v>1.6071230000000001</v>
+      </c>
+      <c r="J62">
+        <v>22.637614679999999</v>
+      </c>
+      <c r="K62">
+        <v>160</v>
+      </c>
+      <c r="L62" t="s">
+        <v>30</v>
+      </c>
+      <c r="M62">
+        <v>4935</v>
+      </c>
+      <c r="N62" t="s">
+        <v>126</v>
+      </c>
+      <c r="O62">
+        <v>5641</v>
+      </c>
+      <c r="P62">
+        <v>874.84488599999997</v>
+      </c>
+      <c r="Q62">
+        <v>218</v>
+      </c>
+      <c r="S62">
+        <v>22.637615</v>
+      </c>
+      <c r="T62">
+        <v>3.864563</v>
+      </c>
+      <c r="U62">
+        <v>292</v>
+      </c>
+      <c r="V62">
+        <v>5.1763870000000001</v>
+      </c>
+      <c r="W62">
+        <v>16.900684999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" t="s">
+        <v>81</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63">
+        <v>188</v>
+      </c>
+      <c r="G63" t="s">
+        <v>39</v>
+      </c>
+      <c r="H63">
+        <v>4165</v>
+      </c>
+      <c r="I63">
+        <v>1.3320529999999999</v>
+      </c>
+      <c r="J63">
+        <v>23.515957449999998</v>
+      </c>
+      <c r="K63" t="s">
+        <v>34</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>4421</v>
+      </c>
+      <c r="N63" t="s">
+        <v>130</v>
+      </c>
+      <c r="O63">
+        <v>5548</v>
+      </c>
+      <c r="P63">
+        <v>796.86373500000002</v>
+      </c>
+      <c r="Q63">
+        <v>188</v>
+      </c>
+      <c r="S63">
+        <v>23.515957</v>
+      </c>
+      <c r="T63">
+        <v>3.3886090000000002</v>
+      </c>
+      <c r="U63">
+        <v>210</v>
+      </c>
+      <c r="V63">
+        <v>3.785148</v>
+      </c>
+      <c r="W63">
+        <v>21.052381</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" t="s">
+        <v>81</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64">
+        <v>214</v>
+      </c>
+      <c r="G64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64">
+        <v>5257</v>
+      </c>
+      <c r="I64">
+        <v>1.2834319999999999</v>
+      </c>
+      <c r="J64">
+        <v>21.04672897</v>
+      </c>
+      <c r="K64" t="s">
+        <v>34</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>4504</v>
+      </c>
+      <c r="N64" t="s">
+        <v>130</v>
+      </c>
+      <c r="O64">
+        <v>6747</v>
+      </c>
+      <c r="P64">
+        <v>667.55595100000005</v>
+      </c>
+      <c r="Q64">
+        <v>214</v>
+      </c>
+      <c r="S64">
+        <v>21.046728999999999</v>
+      </c>
+      <c r="T64">
+        <v>3.17178</v>
+      </c>
+      <c r="U64">
+        <v>231</v>
+      </c>
+      <c r="V64">
+        <v>3.4237440000000001</v>
+      </c>
+      <c r="W64">
+        <v>19.497836</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D65" t="s">
+        <v>81</v>
+      </c>
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65">
+        <v>107</v>
+      </c>
+      <c r="G65" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65">
+        <v>4061</v>
+      </c>
+      <c r="I65">
+        <v>1.422064</v>
+      </c>
+      <c r="J65">
+        <v>54.570093460000002</v>
+      </c>
+      <c r="K65" t="s">
+        <v>34</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>5839</v>
+      </c>
+      <c r="N65" t="s">
+        <v>35</v>
+      </c>
+      <c r="O65">
+        <v>5775</v>
+      </c>
+      <c r="P65">
+        <v>1011.082251</v>
+      </c>
+      <c r="Q65">
+        <v>107</v>
+      </c>
+      <c r="S65">
+        <v>54.570093</v>
+      </c>
+      <c r="T65">
+        <v>1.852814</v>
+      </c>
+      <c r="U65">
+        <v>147</v>
+      </c>
+      <c r="V65">
+        <v>2.545455</v>
+      </c>
+      <c r="W65">
+        <v>39.721088000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" t="s">
+        <v>81</v>
+      </c>
+      <c r="E66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <v>114</v>
+      </c>
+      <c r="G66" t="s">
+        <v>39</v>
+      </c>
+      <c r="H66">
+        <v>2338</v>
+      </c>
+      <c r="I66">
+        <v>1.200599</v>
+      </c>
+      <c r="J66">
+        <v>33.026315789999998</v>
+      </c>
+      <c r="K66" t="s">
+        <v>34</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>3765</v>
+      </c>
+      <c r="N66" t="s">
+        <v>130</v>
+      </c>
+      <c r="O66">
+        <v>2807</v>
+      </c>
+      <c r="P66">
+        <v>1341.2896330000001</v>
+      </c>
+      <c r="Q66">
+        <v>114</v>
+      </c>
+      <c r="S66">
+        <v>33.026316000000001</v>
+      </c>
+      <c r="T66">
+        <v>4.0612750000000002</v>
+      </c>
+      <c r="U66">
+        <v>125</v>
+      </c>
+      <c r="V66">
+        <v>4.4531530000000004</v>
+      </c>
+      <c r="W66">
+        <v>30.12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67">
+        <v>326</v>
+      </c>
+      <c r="G67" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67">
+        <v>4795</v>
+      </c>
+      <c r="I67">
+        <v>1.309906</v>
+      </c>
+      <c r="J67">
+        <v>17.659509199999999</v>
+      </c>
+      <c r="K67" t="s">
+        <v>34</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>5757</v>
+      </c>
+      <c r="N67" t="s">
+        <v>35</v>
+      </c>
+      <c r="O67">
+        <v>6281</v>
+      </c>
+      <c r="P67">
+        <v>916.57379400000002</v>
+      </c>
+      <c r="Q67">
+        <v>326</v>
+      </c>
+      <c r="S67">
+        <v>17.659509</v>
+      </c>
+      <c r="T67">
+        <v>5.1902559999999998</v>
+      </c>
+      <c r="U67">
+        <v>366</v>
+      </c>
+      <c r="V67">
+        <v>5.8270980000000003</v>
+      </c>
+      <c r="W67">
+        <v>15.729507999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" t="s">
+        <v>81</v>
+      </c>
+      <c r="E68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68">
+        <v>154</v>
+      </c>
+      <c r="G68" t="s">
+        <v>39</v>
+      </c>
+      <c r="H68">
+        <v>4505</v>
+      </c>
+      <c r="I68">
+        <v>1.3658159999999999</v>
+      </c>
+      <c r="J68">
+        <v>37.967532470000002</v>
+      </c>
+      <c r="K68" t="s">
+        <v>34</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>5847</v>
+      </c>
+      <c r="N68" t="s">
+        <v>35</v>
+      </c>
+      <c r="O68">
+        <v>6153</v>
+      </c>
+      <c r="P68">
+        <v>950.26816199999996</v>
+      </c>
+      <c r="Q68">
+        <v>154</v>
+      </c>
+      <c r="S68">
+        <v>37.967531999999999</v>
+      </c>
+      <c r="T68">
+        <v>2.5028440000000001</v>
+      </c>
+      <c r="U68">
+        <v>174</v>
+      </c>
+      <c r="V68">
+        <v>2.8278889999999999</v>
+      </c>
+      <c r="W68">
+        <v>33.603448</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" t="s">
+        <v>81</v>
+      </c>
+      <c r="E69" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69">
+        <v>115</v>
+      </c>
+      <c r="G69" t="s">
+        <v>39</v>
+      </c>
+      <c r="H69">
+        <v>3010</v>
+      </c>
+      <c r="I69">
+        <v>1.6106309999999999</v>
+      </c>
+      <c r="J69">
+        <v>51.547826090000001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>34</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>5928</v>
+      </c>
+      <c r="N69" t="s">
+        <v>35</v>
+      </c>
+      <c r="O69">
+        <v>4848</v>
+      </c>
+      <c r="P69">
+        <v>1222.772277</v>
+      </c>
+      <c r="Q69">
+        <v>115</v>
+      </c>
+      <c r="S69">
+        <v>51.547826000000001</v>
+      </c>
+      <c r="T69">
+        <v>2.372112</v>
+      </c>
+      <c r="U69">
+        <v>130</v>
+      </c>
+      <c r="V69">
+        <v>2.6815180000000001</v>
+      </c>
+      <c r="W69">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" t="s">
+        <v>81</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70">
+        <v>224</v>
+      </c>
+      <c r="G70" t="s">
+        <v>39</v>
+      </c>
+      <c r="H70">
+        <v>4211</v>
+      </c>
+      <c r="I70">
+        <v>1.3402989999999999</v>
+      </c>
+      <c r="J70">
+        <v>26.178571430000002</v>
+      </c>
+      <c r="K70" t="s">
+        <v>34</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>5864</v>
+      </c>
+      <c r="N70" t="s">
+        <v>86</v>
+      </c>
+      <c r="O70">
+        <v>5644</v>
+      </c>
+      <c r="P70">
+        <v>1038.9794469999999</v>
+      </c>
+      <c r="Q70">
+        <v>224</v>
+      </c>
+      <c r="S70">
+        <v>26.178571000000002</v>
+      </c>
+      <c r="T70">
+        <v>3.9688159999999999</v>
+      </c>
+      <c r="U70">
+        <v>248</v>
+      </c>
+      <c r="V70">
+        <v>4.3940469999999996</v>
+      </c>
+      <c r="W70">
+        <v>23.645161000000002</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>138</v>
+      </c>
+      <c r="D71" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71">
+        <v>284</v>
+      </c>
+      <c r="G71" t="s">
+        <v>39</v>
+      </c>
+      <c r="H71">
+        <v>3259</v>
+      </c>
+      <c r="I71">
+        <v>1.379257</v>
+      </c>
+      <c r="J71">
+        <v>17.352112680000001</v>
+      </c>
+      <c r="K71">
+        <v>160</v>
+      </c>
+      <c r="L71" t="s">
+        <v>30</v>
+      </c>
+      <c r="M71">
+        <v>4928</v>
+      </c>
+      <c r="N71" t="s">
+        <v>79</v>
+      </c>
+      <c r="O71">
+        <v>4495</v>
+      </c>
+      <c r="P71">
+        <v>1096.3292550000001</v>
+      </c>
+      <c r="Q71">
+        <v>284</v>
+      </c>
+      <c r="S71">
+        <v>17.352112999999999</v>
+      </c>
+      <c r="T71">
+        <v>6.3181310000000002</v>
+      </c>
+      <c r="U71">
+        <v>318</v>
+      </c>
+      <c r="V71">
+        <v>7.0745269999999998</v>
+      </c>
+      <c r="W71">
+        <v>15.496855</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>139</v>
+      </c>
+      <c r="D72" t="s">
+        <v>81</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72">
+        <v>103</v>
+      </c>
+      <c r="G72" t="s">
+        <v>39</v>
+      </c>
+      <c r="H72">
+        <v>2141</v>
+      </c>
+      <c r="I72">
+        <v>1.1704810000000001</v>
+      </c>
+      <c r="J72">
+        <v>47.543689319999999</v>
+      </c>
+      <c r="K72">
+        <v>160</v>
+      </c>
+      <c r="L72" t="s">
+        <v>30</v>
+      </c>
+      <c r="M72">
+        <v>4897</v>
+      </c>
+      <c r="N72" t="s">
+        <v>140</v>
+      </c>
+      <c r="O72">
+        <v>2506</v>
+      </c>
+      <c r="P72">
+        <v>1954.110136</v>
+      </c>
+      <c r="Q72">
+        <v>103</v>
+      </c>
+      <c r="S72">
+        <v>47.543689000000001</v>
+      </c>
+      <c r="T72">
+        <v>4.1101359999999998</v>
+      </c>
+      <c r="U72">
+        <v>106</v>
+      </c>
+      <c r="V72">
+        <v>4.2298479999999996</v>
+      </c>
+      <c r="W72">
+        <v>46.198112999999999</v>
+      </c>
+      <c r="X72">
+        <v>73</v>
+      </c>
+      <c r="Y72">
+        <v>67.082192000000006</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73">
+        <v>204</v>
+      </c>
+      <c r="G73" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73">
+        <v>3113</v>
+      </c>
+      <c r="I73">
+        <v>1.49213</v>
+      </c>
+      <c r="J73">
+        <v>24.078431370000001</v>
+      </c>
+      <c r="K73">
+        <v>160</v>
+      </c>
+      <c r="L73" t="s">
+        <v>30</v>
+      </c>
+      <c r="M73">
+        <v>4912</v>
+      </c>
+      <c r="N73" t="s">
+        <v>112</v>
+      </c>
+      <c r="O73">
+        <v>4645</v>
+      </c>
+      <c r="P73">
+        <v>1057.4811629999999</v>
+      </c>
+      <c r="Q73">
+        <v>204</v>
+      </c>
+      <c r="S73">
+        <v>24.078430999999998</v>
+      </c>
+      <c r="T73">
+        <v>4.3918189999999999</v>
+      </c>
+      <c r="U73">
+        <v>217</v>
+      </c>
+      <c r="V73">
+        <v>4.6716899999999999</v>
+      </c>
+      <c r="W73">
+        <v>22.635945</v>
+      </c>
+      <c r="X73">
+        <v>176</v>
+      </c>
+      <c r="Y73">
+        <v>27.909091</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" t="s">
+        <v>81</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74">
+        <v>207</v>
+      </c>
+      <c r="G74" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74">
+        <v>4607</v>
+      </c>
+      <c r="I74">
+        <v>1.3179940000000001</v>
+      </c>
+      <c r="J74">
+        <v>23.811594199999998</v>
+      </c>
+      <c r="K74">
+        <v>160</v>
+      </c>
+      <c r="L74" t="s">
+        <v>30</v>
+      </c>
+      <c r="M74">
+        <v>4929</v>
+      </c>
+      <c r="N74" t="s">
+        <v>112</v>
+      </c>
+      <c r="O74">
+        <v>6072</v>
+      </c>
+      <c r="P74">
+        <v>811.75889299999994</v>
+      </c>
+      <c r="Q74">
+        <v>207</v>
+      </c>
+      <c r="S74">
+        <v>23.811593999999999</v>
+      </c>
+      <c r="T74">
+        <v>3.4090910000000001</v>
+      </c>
+      <c r="U74">
+        <v>238</v>
+      </c>
+      <c r="V74">
+        <v>3.9196309999999999</v>
+      </c>
+      <c r="W74">
+        <v>20.710083999999998</v>
+      </c>
+      <c r="X74">
+        <v>174</v>
+      </c>
+      <c r="Y74">
+        <v>28.327586</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" t="s">
+        <v>81</v>
+      </c>
+      <c r="E75" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75">
+        <v>308</v>
+      </c>
+      <c r="G75" t="s">
+        <v>39</v>
+      </c>
+      <c r="H75">
+        <v>4235</v>
+      </c>
+      <c r="I75">
+        <v>1.7157020000000001</v>
+      </c>
+      <c r="J75">
+        <v>16.02597403</v>
+      </c>
+      <c r="K75">
+        <v>160</v>
+      </c>
+      <c r="L75" t="s">
+        <v>30</v>
+      </c>
+      <c r="M75">
+        <v>4936</v>
+      </c>
+      <c r="N75" t="s">
+        <v>112</v>
+      </c>
+      <c r="O75">
+        <v>7266</v>
+      </c>
+      <c r="P75">
+        <v>679.32837900000004</v>
+      </c>
+      <c r="Q75">
+        <v>308</v>
+      </c>
+      <c r="S75">
+        <v>16.025974000000001</v>
+      </c>
+      <c r="T75">
+        <v>4.2389210000000004</v>
+      </c>
+      <c r="U75">
+        <v>408</v>
+      </c>
+      <c r="V75">
+        <v>5.6151939999999998</v>
+      </c>
+      <c r="W75">
+        <v>12.098039</v>
+      </c>
+      <c r="X75">
+        <v>18</v>
+      </c>
+      <c r="Y75">
+        <v>274.22222199999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" t="s">
+        <v>81</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76">
+        <v>172</v>
+      </c>
+      <c r="G76" t="s">
+        <v>39</v>
+      </c>
+      <c r="H76">
+        <v>3867</v>
+      </c>
+      <c r="I76">
+        <v>1.468839</v>
+      </c>
+      <c r="J76">
+        <v>28.674418599999999</v>
+      </c>
+      <c r="K76">
+        <v>160</v>
+      </c>
+      <c r="L76" t="s">
+        <v>30</v>
+      </c>
+      <c r="M76">
+        <v>4932</v>
+      </c>
+      <c r="N76" t="s">
+        <v>112</v>
+      </c>
+      <c r="O76">
+        <v>5680</v>
+      </c>
+      <c r="P76">
+        <v>868.30985899999996</v>
+      </c>
+      <c r="Q76">
+        <v>172</v>
+      </c>
+      <c r="S76">
+        <v>28.674419</v>
+      </c>
+      <c r="T76">
+        <v>3.0281690000000001</v>
+      </c>
+      <c r="U76">
+        <v>204</v>
+      </c>
+      <c r="V76">
+        <v>3.5915490000000001</v>
+      </c>
+      <c r="W76">
+        <v>24.176470999999999</v>
+      </c>
+      <c r="X76">
+        <v>4</v>
+      </c>
+      <c r="Y76">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" t="s">
+        <v>81</v>
+      </c>
+      <c r="E77" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77">
+        <v>321</v>
+      </c>
+      <c r="G77" t="s">
+        <v>39</v>
+      </c>
+      <c r="H77">
+        <v>5559</v>
+      </c>
+      <c r="I77">
+        <v>1.3502430000000001</v>
+      </c>
+      <c r="J77">
+        <v>15.383177570000001</v>
+      </c>
+      <c r="K77">
+        <v>160</v>
+      </c>
+      <c r="L77" t="s">
+        <v>30</v>
+      </c>
+      <c r="M77">
+        <v>4938</v>
+      </c>
+      <c r="N77" t="s">
+        <v>112</v>
+      </c>
+      <c r="O77">
+        <v>7506</v>
+      </c>
+      <c r="P77">
+        <v>657.87370099999998</v>
+      </c>
+      <c r="Q77">
+        <v>321</v>
+      </c>
+      <c r="S77">
+        <v>15.383177999999999</v>
+      </c>
+      <c r="T77">
+        <v>4.2765789999999999</v>
+      </c>
+      <c r="U77">
+        <v>392</v>
+      </c>
+      <c r="V77">
+        <v>5.2224890000000004</v>
+      </c>
+      <c r="W77">
+        <v>12.596939000000001</v>
+      </c>
+      <c r="X77">
+        <v>279</v>
+      </c>
+      <c r="Y77">
+        <v>17.698924999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>146</v>
+      </c>
+      <c r="D78" t="s">
+        <v>81</v>
+      </c>
+      <c r="E78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78">
+        <v>272</v>
+      </c>
+      <c r="G78" t="s">
+        <v>39</v>
+      </c>
+      <c r="H78">
+        <v>5772</v>
+      </c>
+      <c r="I78">
+        <v>1.1971590000000001</v>
+      </c>
+      <c r="J78">
+        <v>18.132352940000001</v>
+      </c>
+      <c r="K78">
+        <v>160</v>
+      </c>
+      <c r="L78" t="s">
+        <v>30</v>
+      </c>
+      <c r="M78">
+        <v>4932</v>
+      </c>
+      <c r="N78" t="s">
+        <v>112</v>
+      </c>
+      <c r="O78">
+        <v>6910</v>
+      </c>
+      <c r="P78">
+        <v>713.74819100000002</v>
+      </c>
+      <c r="Q78">
+        <v>272</v>
+      </c>
+      <c r="S78">
+        <v>18.132352999999998</v>
+      </c>
+      <c r="T78">
+        <v>3.9363239999999999</v>
+      </c>
+      <c r="U78">
+        <v>367</v>
+      </c>
+      <c r="V78">
+        <v>5.3111430000000004</v>
+      </c>
+      <c r="W78">
+        <v>13.438692</v>
+      </c>
+      <c r="X78">
+        <v>227</v>
+      </c>
+      <c r="Y78">
+        <v>21.726872</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>147</v>
+      </c>
+      <c r="D79" t="s">
+        <v>81</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79">
+        <v>52</v>
+      </c>
+      <c r="G79" t="s">
+        <v>39</v>
+      </c>
+      <c r="H79">
+        <v>2135</v>
+      </c>
+      <c r="I79">
+        <v>1.7639339999999999</v>
+      </c>
+      <c r="J79">
+        <v>94.096153849999993</v>
+      </c>
+      <c r="K79">
+        <v>160</v>
+      </c>
+      <c r="L79" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79">
+        <v>4893</v>
+      </c>
+      <c r="N79" t="s">
+        <v>112</v>
+      </c>
+      <c r="O79">
+        <v>3766</v>
+      </c>
+      <c r="P79">
+        <v>1299.2565059999999</v>
+      </c>
+      <c r="Q79">
+        <v>52</v>
+      </c>
+      <c r="S79">
+        <v>94.096153999999999</v>
+      </c>
+      <c r="T79">
+        <v>1.3807750000000001</v>
+      </c>
+      <c r="U79">
+        <v>55</v>
+      </c>
+      <c r="V79">
+        <v>1.4604349999999999</v>
+      </c>
+      <c r="W79">
+        <v>88.963635999999994</v>
+      </c>
+      <c r="X79">
+        <v>44</v>
+      </c>
+      <c r="Y79">
+        <v>111.204545</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s">
+        <v>148</v>
+      </c>
+      <c r="D80" t="s">
+        <v>81</v>
+      </c>
+      <c r="E80" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80">
+        <v>636</v>
+      </c>
+      <c r="G80" t="s">
+        <v>39</v>
+      </c>
+      <c r="H80">
+        <v>8618</v>
+      </c>
+      <c r="I80">
+        <v>1.1698770000000001</v>
+      </c>
+      <c r="J80">
+        <v>7.7484276699999999</v>
+      </c>
+      <c r="K80">
+        <v>160</v>
+      </c>
+      <c r="L80" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80">
+        <v>4928</v>
+      </c>
+      <c r="N80" t="s">
+        <v>112</v>
+      </c>
+      <c r="O80">
+        <v>10082</v>
+      </c>
+      <c r="P80">
+        <v>488.79190599999998</v>
+      </c>
+      <c r="Q80">
+        <v>636</v>
+      </c>
+      <c r="S80">
+        <v>7.7484279999999996</v>
+      </c>
+      <c r="T80">
+        <v>6.3082719999999997</v>
+      </c>
+      <c r="U80">
+        <v>710</v>
+      </c>
+      <c r="V80">
+        <v>7.0422539999999998</v>
+      </c>
+      <c r="W80">
+        <v>6.9408450000000004</v>
+      </c>
+      <c r="X80">
+        <v>527</v>
+      </c>
+      <c r="Y80">
+        <v>9.3510439999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" t="s">
+        <v>81</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81">
+        <v>283</v>
+      </c>
+      <c r="G81" t="s">
+        <v>39</v>
+      </c>
+      <c r="H81">
+        <v>4299</v>
+      </c>
+      <c r="I81">
+        <v>1.3037920000000001</v>
+      </c>
+      <c r="J81">
+        <v>17.441696109999999</v>
+      </c>
+      <c r="K81">
+        <v>160</v>
+      </c>
+      <c r="L81" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81">
+        <v>4936</v>
+      </c>
+      <c r="N81" t="s">
+        <v>112</v>
+      </c>
+      <c r="O81">
+        <v>5605</v>
+      </c>
+      <c r="P81">
+        <v>880.64228400000002</v>
+      </c>
+      <c r="Q81">
+        <v>283</v>
+      </c>
+      <c r="S81">
+        <v>17.441696</v>
+      </c>
+      <c r="T81">
+        <v>5.0490630000000003</v>
+      </c>
+      <c r="U81">
+        <v>287</v>
+      </c>
+      <c r="V81">
+        <v>5.1204280000000004</v>
+      </c>
+      <c r="W81">
+        <v>17.198606000000002</v>
+      </c>
+      <c r="X81">
+        <v>90</v>
+      </c>
+      <c r="Y81">
+        <v>54.844444000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>150</v>
+      </c>
+      <c r="D82" t="s">
+        <v>81</v>
+      </c>
+      <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82">
+        <v>190</v>
+      </c>
+      <c r="G82" t="s">
+        <v>39</v>
+      </c>
+      <c r="H82">
+        <v>5244</v>
+      </c>
+      <c r="I82">
+        <v>1.3251329999999999</v>
+      </c>
+      <c r="J82">
+        <v>25.952631579999998</v>
+      </c>
+      <c r="K82">
+        <v>160</v>
+      </c>
+      <c r="L82" t="s">
+        <v>30</v>
+      </c>
+      <c r="M82">
+        <v>4931</v>
+      </c>
+      <c r="N82" t="s">
+        <v>112</v>
+      </c>
+      <c r="O82">
+        <v>6949</v>
+      </c>
+      <c r="P82">
+        <v>709.59850300000005</v>
+      </c>
+      <c r="Q82">
+        <v>190</v>
+      </c>
+      <c r="S82">
+        <v>25.952632000000001</v>
+      </c>
+      <c r="T82">
+        <v>2.7342059999999999</v>
+      </c>
+      <c r="U82">
+        <v>230</v>
+      </c>
+      <c r="V82">
+        <v>3.3098290000000001</v>
+      </c>
+      <c r="W82">
+        <v>21.439129999999999</v>
+      </c>
+      <c r="X82">
+        <v>147</v>
+      </c>
+      <c r="Y82">
+        <v>33.544218000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>151</v>
+      </c>
+      <c r="D83" t="s">
+        <v>81</v>
+      </c>
+      <c r="E83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83">
+        <v>82</v>
+      </c>
+      <c r="G83" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83">
+        <v>4032</v>
+      </c>
+      <c r="I83">
+        <v>1.386409</v>
+      </c>
+      <c r="J83">
+        <v>60.170731709999998</v>
+      </c>
+      <c r="K83">
+        <v>160</v>
+      </c>
+      <c r="L83" t="s">
+        <v>30</v>
+      </c>
+      <c r="M83">
+        <v>4934</v>
+      </c>
+      <c r="N83" t="s">
+        <v>112</v>
+      </c>
+      <c r="O83">
+        <v>5590</v>
+      </c>
+      <c r="P83">
+        <v>882.64758500000005</v>
+      </c>
+      <c r="Q83">
+        <v>82</v>
+      </c>
+      <c r="S83">
+        <v>60.170732000000001</v>
+      </c>
+      <c r="T83">
+        <v>1.4669049999999999</v>
+      </c>
+      <c r="U83">
+        <v>95</v>
+      </c>
+      <c r="V83">
+        <v>1.6994629999999999</v>
+      </c>
+      <c r="W83">
+        <v>51.936841999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84" t="s">
+        <v>81</v>
+      </c>
+      <c r="E84" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84">
+        <v>384</v>
+      </c>
+      <c r="G84" t="s">
+        <v>39</v>
+      </c>
+      <c r="H84">
+        <v>5315</v>
+      </c>
+      <c r="I84">
+        <v>1.2250239999999999</v>
+      </c>
+      <c r="J84">
+        <v>12.90364583</v>
+      </c>
+      <c r="K84">
+        <v>160</v>
+      </c>
+      <c r="L84" t="s">
+        <v>30</v>
+      </c>
+      <c r="M84">
+        <v>4955</v>
+      </c>
+      <c r="N84" t="s">
+        <v>112</v>
+      </c>
+      <c r="O84">
+        <v>6511</v>
+      </c>
+      <c r="P84">
+        <v>761.019813</v>
+      </c>
+      <c r="Q84">
+        <v>384</v>
+      </c>
+      <c r="S84">
+        <v>12.903646</v>
+      </c>
+      <c r="T84">
+        <v>5.8977120000000003</v>
+      </c>
+      <c r="U84">
+        <v>436</v>
+      </c>
+      <c r="V84">
+        <v>6.6963600000000003</v>
+      </c>
+      <c r="W84">
+        <v>11.364679000000001</v>
+      </c>
+      <c r="X84">
+        <v>325</v>
+      </c>
+      <c r="Y84">
+        <v>15.246154000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>153</v>
+      </c>
+      <c r="D85" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" t="s">
+        <v>29</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>160</v>
+      </c>
+      <c r="L85" t="s">
+        <v>30</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85" t="s">
+        <v>154</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>155</v>
+      </c>
+      <c r="D86" t="s">
+        <v>156</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86">
+        <v>148</v>
+      </c>
+      <c r="G86" t="s">
+        <v>39</v>
+      </c>
+      <c r="H86">
+        <v>2184</v>
+      </c>
+      <c r="I86">
+        <v>1.284799</v>
+      </c>
+      <c r="J86">
+        <v>33.378378380000001</v>
+      </c>
+      <c r="K86">
+        <v>160</v>
+      </c>
+      <c r="L86" t="s">
+        <v>30</v>
+      </c>
+      <c r="M86">
+        <v>4940</v>
+      </c>
+      <c r="N86" t="s">
+        <v>157</v>
+      </c>
+      <c r="O86">
+        <v>2806</v>
+      </c>
+      <c r="P86">
+        <v>1760.5131859999999</v>
+      </c>
+      <c r="Q86">
+        <v>148</v>
+      </c>
+      <c r="S86">
+        <v>33.378377999999998</v>
+      </c>
+      <c r="T86">
+        <v>5.2744119999999999</v>
+      </c>
+      <c r="U86">
+        <v>155</v>
+      </c>
+      <c r="V86">
+        <v>5.5238769999999997</v>
+      </c>
+      <c r="W86">
+        <v>31.870968000000001</v>
+      </c>
+      <c r="X86">
+        <v>125</v>
+      </c>
+      <c r="Y86">
+        <v>39.520000000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>158</v>
+      </c>
+      <c r="D87" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87">
+        <v>140</v>
+      </c>
+      <c r="G87" t="s">
+        <v>39</v>
+      </c>
+      <c r="H87">
+        <v>3538</v>
+      </c>
+      <c r="I87">
+        <v>1.3326739999999999</v>
+      </c>
+      <c r="J87">
+        <v>35.228571430000002</v>
+      </c>
+      <c r="K87">
+        <v>160</v>
+      </c>
+      <c r="L87" t="s">
+        <v>30</v>
+      </c>
+      <c r="M87">
+        <v>4932</v>
+      </c>
+      <c r="N87" t="s">
+        <v>97</v>
+      </c>
+      <c r="O87">
+        <v>4715</v>
+      </c>
+      <c r="P87">
+        <v>1046.02333</v>
+      </c>
+      <c r="Q87">
+        <v>140</v>
+      </c>
+      <c r="S87">
+        <v>35.228571000000002</v>
+      </c>
+      <c r="T87">
+        <v>2.9692470000000002</v>
+      </c>
+      <c r="U87">
+        <v>172</v>
+      </c>
+      <c r="V87">
+        <v>3.647932</v>
+      </c>
+      <c r="W87">
+        <v>28.674419</v>
+      </c>
+      <c r="X87">
+        <v>11</v>
+      </c>
+      <c r="Y87">
+        <v>448.36363599999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>158</v>
+      </c>
+      <c r="D88" t="s">
+        <v>38</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88">
+        <v>156</v>
+      </c>
+      <c r="G88" t="s">
+        <v>39</v>
+      </c>
+      <c r="H88">
+        <v>3376</v>
+      </c>
+      <c r="I88">
+        <v>1.3062800000000001</v>
+      </c>
+      <c r="J88">
+        <v>31.717948719999999</v>
+      </c>
+      <c r="K88">
+        <v>160</v>
+      </c>
+      <c r="L88" t="s">
+        <v>30</v>
+      </c>
+      <c r="M88">
+        <v>4948</v>
+      </c>
+      <c r="N88" t="s">
+        <v>97</v>
+      </c>
+      <c r="O88">
+        <v>4410</v>
+      </c>
+      <c r="P88">
+        <v>1121.995465</v>
+      </c>
+      <c r="Q88">
+        <v>156</v>
+      </c>
+      <c r="S88">
+        <v>31.717949000000001</v>
+      </c>
+      <c r="T88">
+        <v>3.5374150000000002</v>
+      </c>
+      <c r="U88">
+        <v>187</v>
+      </c>
+      <c r="V88">
+        <v>4.2403630000000003</v>
+      </c>
+      <c r="W88">
+        <v>26.459893000000001</v>
+      </c>
+      <c r="X88">
+        <v>133</v>
+      </c>
+      <c r="Y88">
+        <v>37.203007999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>159</v>
+      </c>
+      <c r="D89" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89">
+        <v>218</v>
+      </c>
+      <c r="G89" t="s">
+        <v>39</v>
+      </c>
+      <c r="H89">
+        <v>2598</v>
+      </c>
+      <c r="I89">
+        <v>1.5496540000000001</v>
+      </c>
+      <c r="J89">
+        <v>22.711009170000001</v>
+      </c>
+      <c r="K89">
+        <v>160</v>
+      </c>
+      <c r="L89" t="s">
+        <v>30</v>
+      </c>
+      <c r="M89">
+        <v>4951</v>
+      </c>
+      <c r="N89" t="s">
+        <v>97</v>
+      </c>
+      <c r="O89">
+        <v>4026</v>
+      </c>
+      <c r="P89">
+        <v>1229.756582</v>
+      </c>
+      <c r="Q89">
+        <v>218</v>
+      </c>
+      <c r="S89">
+        <v>22.711009000000001</v>
+      </c>
+      <c r="T89">
+        <v>5.4148040000000002</v>
+      </c>
+      <c r="U89">
+        <v>222</v>
+      </c>
+      <c r="V89">
+        <v>5.5141580000000001</v>
+      </c>
+      <c r="W89">
+        <v>22.301801999999999</v>
+      </c>
+      <c r="X89">
+        <v>178</v>
+      </c>
+      <c r="Y89">
+        <v>27.814606999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>160</v>
+      </c>
+      <c r="D90" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90">
+        <v>175</v>
+      </c>
+      <c r="G90" t="s">
+        <v>39</v>
+      </c>
+      <c r="H90">
+        <v>3329</v>
+      </c>
+      <c r="I90">
+        <v>1.3730850000000001</v>
+      </c>
+      <c r="J90">
+        <v>28.234285710000002</v>
+      </c>
+      <c r="K90">
+        <v>160</v>
+      </c>
+      <c r="L90" t="s">
+        <v>30</v>
+      </c>
+      <c r="M90">
+        <v>4941</v>
+      </c>
+      <c r="N90" t="s">
+        <v>97</v>
+      </c>
+      <c r="O90">
+        <v>4571</v>
+      </c>
+      <c r="P90">
+        <v>1080.9450890000001</v>
+      </c>
+      <c r="Q90">
+        <v>175</v>
+      </c>
+      <c r="S90">
+        <v>28.234286000000001</v>
+      </c>
+      <c r="T90">
+        <v>3.828484</v>
+      </c>
+      <c r="U90">
+        <v>254</v>
+      </c>
+      <c r="V90">
+        <v>5.5567710000000003</v>
+      </c>
+      <c r="W90">
+        <v>19.452756000000001</v>
+      </c>
+      <c r="X90">
+        <v>161</v>
+      </c>
+      <c r="Y90">
+        <v>30.689440999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>161</v>
+      </c>
+      <c r="D91" t="s">
+        <v>38</v>
+      </c>
+      <c r="E91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91">
+        <v>142</v>
+      </c>
+      <c r="G91" t="s">
+        <v>39</v>
+      </c>
+      <c r="H91">
+        <v>4235</v>
+      </c>
+      <c r="I91">
+        <v>1.3971659999999999</v>
+      </c>
+      <c r="J91">
+        <v>34.718309859999998</v>
+      </c>
+      <c r="K91">
+        <v>160</v>
+      </c>
+      <c r="L91" t="s">
+        <v>30</v>
+      </c>
+      <c r="M91">
+        <v>4930</v>
+      </c>
+      <c r="N91" t="s">
+        <v>97</v>
+      </c>
+      <c r="O91">
+        <v>5917</v>
+      </c>
+      <c r="P91">
+        <v>833.19249600000001</v>
+      </c>
+      <c r="Q91">
+        <v>142</v>
+      </c>
+      <c r="S91">
+        <v>34.718310000000002</v>
+      </c>
+      <c r="T91">
+        <v>2.3998650000000001</v>
+      </c>
+      <c r="U91">
+        <v>185</v>
+      </c>
+      <c r="V91">
+        <v>3.1265839999999998</v>
+      </c>
+      <c r="W91">
+        <v>26.648648999999999</v>
+      </c>
+      <c r="X91">
+        <v>124</v>
+      </c>
+      <c r="Y91">
+        <v>39.758065000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>162</v>
+      </c>
+      <c r="D92" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92" t="s">
+        <v>29</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>160</v>
+      </c>
+      <c r="L92" t="s">
+        <v>30</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92" t="s">
+        <v>97</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="U92">
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>163</v>
+      </c>
+      <c r="D93" t="s">
+        <v>28</v>
+      </c>
+      <c r="E93" t="s">
+        <v>29</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>160</v>
+      </c>
+      <c r="L93" t="s">
+        <v>30</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93" t="s">
+        <v>97</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="U93">
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s">
+        <v>164</v>
+      </c>
+      <c r="D94" t="s">
+        <v>38</v>
+      </c>
+      <c r="E94" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94">
+        <v>412</v>
+      </c>
+      <c r="G94" t="s">
+        <v>39</v>
+      </c>
+      <c r="H94">
+        <v>3032</v>
+      </c>
+      <c r="I94">
+        <v>1.4267810000000001</v>
+      </c>
+      <c r="J94">
+        <v>11.9538835</v>
+      </c>
+      <c r="K94">
+        <v>160</v>
+      </c>
+      <c r="L94" t="s">
+        <v>30</v>
+      </c>
+      <c r="M94">
+        <v>4925</v>
+      </c>
+      <c r="N94" t="s">
+        <v>165</v>
+      </c>
+      <c r="O94">
+        <v>4326</v>
+      </c>
+      <c r="P94">
+        <v>1138.465095</v>
+      </c>
+      <c r="Q94">
+        <v>412</v>
+      </c>
+      <c r="S94">
+        <v>11.953884</v>
+      </c>
+      <c r="T94">
+        <v>9.5238099999999992</v>
+      </c>
+      <c r="U94">
+        <v>478</v>
+      </c>
+      <c r="V94">
+        <v>11.049467999999999</v>
+      </c>
+      <c r="W94">
+        <v>10.303347</v>
+      </c>
+      <c r="X94">
+        <v>3</v>
+      </c>
+      <c r="Y94">
+        <v>1641.666667</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="s">
+        <v>166</v>
+      </c>
+      <c r="D95" t="s">
+        <v>38</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95">
+        <v>64</v>
+      </c>
+      <c r="G95" t="s">
+        <v>39</v>
+      </c>
+      <c r="H95">
+        <v>2099</v>
+      </c>
+      <c r="I95">
+        <v>2.113864</v>
+      </c>
+      <c r="J95">
+        <v>75.90625</v>
+      </c>
+      <c r="K95">
+        <v>160</v>
+      </c>
+      <c r="L95" t="s">
+        <v>30</v>
+      </c>
+      <c r="M95">
+        <v>4858</v>
+      </c>
+      <c r="N95" t="s">
+        <v>97</v>
+      </c>
+      <c r="O95">
+        <v>4437</v>
+      </c>
+      <c r="P95">
+        <v>1094.8839310000001</v>
+      </c>
+      <c r="Q95">
+        <v>64</v>
+      </c>
+      <c r="S95">
+        <v>75.90625</v>
+      </c>
+      <c r="T95">
+        <v>1.4424159999999999</v>
+      </c>
+      <c r="U95">
+        <v>83</v>
+      </c>
+      <c r="V95">
+        <v>1.870633</v>
+      </c>
+      <c r="W95">
+        <v>58.530119999999997</v>
+      </c>
+      <c r="X95">
+        <v>52</v>
+      </c>
+      <c r="Y95">
+        <v>93.423077000000006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" t="s">
+        <v>167</v>
+      </c>
+      <c r="D96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E96" t="s">
+        <v>29</v>
+      </c>
+      <c r="F96">
+        <v>165</v>
+      </c>
+      <c r="G96" t="s">
+        <v>39</v>
+      </c>
+      <c r="H96">
+        <v>2310</v>
+      </c>
+      <c r="I96">
+        <v>1.4623379999999999</v>
+      </c>
+      <c r="J96">
+        <v>29.806060609999999</v>
+      </c>
+      <c r="K96">
+        <v>160</v>
+      </c>
+      <c r="L96" t="s">
+        <v>30</v>
+      </c>
+      <c r="M96">
+        <v>4918</v>
+      </c>
+      <c r="N96" t="s">
+        <v>97</v>
+      </c>
+      <c r="O96">
+        <v>3378</v>
+      </c>
+      <c r="P96">
+        <v>1455.8910599999999</v>
+      </c>
+      <c r="Q96">
+        <v>165</v>
+      </c>
+      <c r="S96">
+        <v>29.806061</v>
+      </c>
+      <c r="T96">
+        <v>4.8845470000000004</v>
+      </c>
+      <c r="U96">
+        <v>181</v>
+      </c>
+      <c r="V96">
+        <v>5.3582000000000001</v>
+      </c>
+      <c r="W96">
+        <v>27.171271000000001</v>
+      </c>
+      <c r="X96">
+        <v>141</v>
+      </c>
+      <c r="Y96">
+        <v>34.879432999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>168</v>
+      </c>
+      <c r="D97" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97">
+        <v>302</v>
+      </c>
+      <c r="G97" t="s">
+        <v>39</v>
+      </c>
+      <c r="H97">
+        <v>4417</v>
+      </c>
+      <c r="I97">
+        <v>1.411365</v>
+      </c>
+      <c r="J97">
+        <v>16.40066225</v>
+      </c>
+      <c r="K97">
+        <v>160</v>
+      </c>
+      <c r="L97" t="s">
+        <v>30</v>
+      </c>
+      <c r="M97">
+        <v>4953</v>
+      </c>
+      <c r="N97" t="s">
+        <v>97</v>
+      </c>
+      <c r="O97">
+        <v>6234</v>
+      </c>
+      <c r="P97">
+        <v>794.51395600000001</v>
+      </c>
+      <c r="Q97">
+        <v>302</v>
+      </c>
+      <c r="S97">
+        <v>16.400662000000001</v>
+      </c>
+      <c r="T97">
+        <v>4.8444019999999997</v>
+      </c>
+      <c r="U97">
+        <v>341</v>
+      </c>
+      <c r="V97">
+        <v>5.4700030000000002</v>
+      </c>
+      <c r="W97">
+        <v>14.524927</v>
+      </c>
+      <c r="X97">
+        <v>261</v>
+      </c>
+      <c r="Y97">
+        <v>18.977011000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
+        <v>169</v>
+      </c>
+      <c r="D98" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98">
+        <v>574</v>
+      </c>
+      <c r="G98" t="s">
+        <v>39</v>
+      </c>
+      <c r="H98">
+        <v>3642</v>
+      </c>
+      <c r="I98">
+        <v>1.346787</v>
+      </c>
+      <c r="J98">
+        <v>8.5958188199999999</v>
+      </c>
+      <c r="K98">
+        <v>160</v>
+      </c>
+      <c r="L98" t="s">
+        <v>30</v>
+      </c>
+      <c r="M98">
+        <v>4934</v>
+      </c>
+      <c r="N98" t="s">
+        <v>97</v>
+      </c>
+      <c r="O98">
+        <v>4905</v>
+      </c>
+      <c r="P98">
+        <v>1005.912334</v>
+      </c>
+      <c r="Q98">
+        <v>574</v>
+      </c>
+      <c r="S98">
+        <v>8.5958190000000005</v>
+      </c>
+      <c r="T98">
+        <v>11.702344999999999</v>
+      </c>
+      <c r="U98">
+        <v>593</v>
+      </c>
+      <c r="V98">
+        <v>12.089703999999999</v>
+      </c>
+      <c r="W98">
+        <v>8.3204049999999992</v>
+      </c>
+      <c r="X98">
+        <v>493</v>
+      </c>
+      <c r="Y98">
+        <v>10.008114000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" t="s">
+        <v>38</v>
+      </c>
+      <c r="E99" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99">
+        <v>271</v>
+      </c>
+      <c r="G99" t="s">
+        <v>39</v>
+      </c>
+      <c r="H99">
+        <v>4243</v>
+      </c>
+      <c r="I99">
+        <v>1.222248</v>
+      </c>
+      <c r="J99">
+        <v>18.19188192</v>
+      </c>
+      <c r="K99">
+        <v>160</v>
+      </c>
+      <c r="L99" t="s">
+        <v>30</v>
+      </c>
+      <c r="M99">
+        <v>4930</v>
+      </c>
+      <c r="N99" t="s">
+        <v>97</v>
+      </c>
+      <c r="O99">
+        <v>5186</v>
+      </c>
+      <c r="P99">
+        <v>950.63632900000005</v>
+      </c>
+      <c r="Q99">
+        <v>271</v>
+      </c>
+      <c r="S99">
+        <v>18.191882</v>
+      </c>
+      <c r="T99">
+        <v>5.2256070000000001</v>
+      </c>
+      <c r="U99">
+        <v>280</v>
+      </c>
+      <c r="V99">
+        <v>5.399152</v>
+      </c>
+      <c r="W99">
+        <v>17.607143000000001</v>
+      </c>
+      <c r="X99">
+        <v>153</v>
+      </c>
+      <c r="Y99">
+        <v>32.222222000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" t="s">
+        <v>171</v>
+      </c>
+      <c r="D100" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100">
+        <v>331</v>
+      </c>
+      <c r="G100" t="s">
+        <v>39</v>
+      </c>
+      <c r="H100">
+        <v>4408</v>
+      </c>
+      <c r="I100">
+        <v>1.3872500000000001</v>
+      </c>
+      <c r="J100">
+        <v>14.87311178</v>
+      </c>
+      <c r="K100">
+        <v>160</v>
+      </c>
+      <c r="L100" t="s">
+        <v>30</v>
+      </c>
+      <c r="M100">
+        <v>4923</v>
+      </c>
+      <c r="N100" t="s">
+        <v>97</v>
+      </c>
+      <c r="O100">
+        <v>6115</v>
+      </c>
+      <c r="P100">
+        <v>805.06950099999995</v>
+      </c>
+      <c r="Q100">
+        <v>331</v>
+      </c>
+      <c r="S100">
+        <v>14.873112000000001</v>
+      </c>
+      <c r="T100">
+        <v>5.4129189999999996</v>
+      </c>
+      <c r="U100">
+        <v>388</v>
+      </c>
+      <c r="V100">
+        <v>6.3450530000000001</v>
+      </c>
+      <c r="W100">
+        <v>12.688143999999999</v>
+      </c>
+      <c r="X100">
+        <v>283</v>
+      </c>
+      <c r="Y100">
+        <v>17.395759999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" t="s">
+        <v>172</v>
+      </c>
+      <c r="D101" t="s">
+        <v>38</v>
+      </c>
+      <c r="E101" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101">
+        <v>149</v>
+      </c>
+      <c r="G101" t="s">
+        <v>39</v>
+      </c>
+      <c r="H101">
+        <v>2291</v>
+      </c>
+      <c r="I101">
+        <v>1.3801829999999999</v>
+      </c>
+      <c r="J101">
+        <v>33.194630869999997</v>
+      </c>
+      <c r="K101">
+        <v>160</v>
+      </c>
+      <c r="L101" t="s">
+        <v>30</v>
+      </c>
+      <c r="M101">
+        <v>4946</v>
+      </c>
+      <c r="N101" t="s">
+        <v>97</v>
+      </c>
+      <c r="O101">
+        <v>3162</v>
+      </c>
+      <c r="P101">
+        <v>1564.1998739999999</v>
+      </c>
+      <c r="Q101">
+        <v>149</v>
+      </c>
+      <c r="S101">
+        <v>33.194631000000001</v>
+      </c>
+      <c r="T101">
+        <v>4.7122070000000003</v>
+      </c>
+      <c r="U101">
+        <v>164</v>
+      </c>
+      <c r="V101">
+        <v>5.186591</v>
+      </c>
+      <c r="W101">
+        <v>30.158536999999999</v>
+      </c>
+      <c r="X101">
+        <v>124</v>
+      </c>
+      <c r="Y101">
+        <v>39.887096999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>173</v>
+      </c>
+      <c r="D102" t="s">
+        <v>38</v>
+      </c>
+      <c r="E102" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102">
+        <v>130</v>
+      </c>
+      <c r="G102" t="s">
+        <v>39</v>
+      </c>
+      <c r="H102">
+        <v>5331</v>
+      </c>
+      <c r="I102">
+        <v>1.2515480000000001</v>
+      </c>
+      <c r="J102">
+        <v>37.815384620000003</v>
+      </c>
+      <c r="K102">
+        <v>160</v>
+      </c>
+      <c r="L102" t="s">
+        <v>30</v>
+      </c>
+      <c r="M102">
+        <v>4916</v>
+      </c>
+      <c r="N102" t="s">
+        <v>97</v>
+      </c>
+      <c r="O102">
+        <v>6672</v>
+      </c>
+      <c r="P102">
+        <v>736.81055200000003</v>
+      </c>
+      <c r="Q102">
+        <v>130</v>
+      </c>
+      <c r="S102">
+        <v>37.815384999999999</v>
+      </c>
+      <c r="T102">
+        <v>1.9484410000000001</v>
+      </c>
+      <c r="U102">
+        <v>184</v>
+      </c>
+      <c r="V102">
+        <v>2.7577940000000001</v>
+      </c>
+      <c r="W102">
+        <v>26.717390999999999</v>
+      </c>
+      <c r="X102">
+        <v>108</v>
+      </c>
+      <c r="Y102">
+        <v>45.518518999999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>174</v>
+      </c>
+      <c r="D103" t="s">
+        <v>28</v>
+      </c>
+      <c r="E103" t="s">
+        <v>29</v>
+      </c>
+      <c r="F103">
+        <v>124</v>
+      </c>
+      <c r="G103" t="s">
+        <v>39</v>
+      </c>
+      <c r="H103">
+        <v>2071</v>
+      </c>
+      <c r="I103">
+        <v>1.3737330000000001</v>
+      </c>
+      <c r="J103">
+        <v>39.862903230000001</v>
+      </c>
+      <c r="K103">
+        <v>160</v>
+      </c>
+      <c r="L103" t="s">
+        <v>30</v>
+      </c>
+      <c r="M103">
+        <v>4943</v>
+      </c>
+      <c r="N103" t="s">
+        <v>97</v>
+      </c>
+      <c r="O103">
+        <v>2845</v>
+      </c>
+      <c r="P103">
+        <v>1737.4340950000001</v>
+      </c>
+      <c r="Q103">
+        <v>124</v>
+      </c>
+      <c r="S103">
+        <v>39.862903000000003</v>
+      </c>
+      <c r="T103">
+        <v>4.3585240000000001</v>
+      </c>
+      <c r="U103">
+        <v>134</v>
+      </c>
+      <c r="V103">
+        <v>4.7100179999999998</v>
+      </c>
+      <c r="W103">
+        <v>36.888060000000003</v>
+      </c>
+      <c r="X103">
+        <v>98</v>
+      </c>
+      <c r="Y103">
+        <v>50.438775999999997</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>175</v>
+      </c>
+      <c r="D104" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" t="s">
+        <v>29</v>
+      </c>
+      <c r="F104">
+        <v>77</v>
+      </c>
+      <c r="G104" t="s">
+        <v>39</v>
+      </c>
+      <c r="H104">
+        <v>2170</v>
+      </c>
+      <c r="I104">
+        <v>1.2050689999999999</v>
+      </c>
+      <c r="J104">
+        <v>64.051948049999993</v>
+      </c>
+      <c r="K104">
+        <v>160</v>
+      </c>
+      <c r="L104" t="s">
+        <v>30</v>
+      </c>
+      <c r="M104">
+        <v>4932</v>
+      </c>
+      <c r="N104" t="s">
+        <v>97</v>
+      </c>
+      <c r="O104">
+        <v>2615</v>
+      </c>
+      <c r="P104">
+        <v>1886.0420650000001</v>
+      </c>
+      <c r="Q104">
+        <v>77</v>
+      </c>
+      <c r="S104">
+        <v>64.051947999999996</v>
+      </c>
+      <c r="T104">
+        <v>2.9445510000000001</v>
+      </c>
+      <c r="U104">
+        <v>76</v>
+      </c>
+      <c r="V104">
+        <v>2.9063099999999999</v>
+      </c>
+      <c r="W104">
+        <v>64.894737000000006</v>
+      </c>
+      <c r="X104">
+        <v>46</v>
+      </c>
+      <c r="Y104">
+        <v>107.21739100000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>176</v>
+      </c>
+      <c r="D105" t="s">
+        <v>38</v>
+      </c>
+      <c r="E105" t="s">
+        <v>29</v>
+      </c>
+      <c r="F105">
+        <v>77</v>
+      </c>
+      <c r="G105" t="s">
+        <v>39</v>
+      </c>
+      <c r="H105">
+        <v>2115</v>
+      </c>
+      <c r="I105">
+        <v>1.178723</v>
+      </c>
+      <c r="J105">
+        <v>64.142857140000004</v>
+      </c>
+      <c r="K105">
+        <v>160</v>
+      </c>
+      <c r="L105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M105">
+        <v>4939</v>
+      </c>
+      <c r="N105" t="s">
+        <v>97</v>
+      </c>
+      <c r="O105">
+        <v>2493</v>
+      </c>
+      <c r="P105">
+        <v>1981.1472120000001</v>
+      </c>
+      <c r="Q105">
+        <v>77</v>
+      </c>
+      <c r="S105">
+        <v>64.142857000000006</v>
+      </c>
+      <c r="T105">
+        <v>3.0886480000000001</v>
+      </c>
+      <c r="U105">
+        <v>81</v>
+      </c>
+      <c r="V105">
+        <v>3.2490969999999999</v>
+      </c>
+      <c r="W105">
+        <v>60.975309000000003</v>
+      </c>
+      <c r="X105">
+        <v>52</v>
+      </c>
+      <c r="Y105">
+        <v>94.980768999999995</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>177</v>
+      </c>
+      <c r="D106" t="s">
+        <v>38</v>
+      </c>
+      <c r="E106" t="s">
+        <v>29</v>
+      </c>
+      <c r="F106">
+        <v>125</v>
+      </c>
+      <c r="G106" t="s">
+        <v>39</v>
+      </c>
+      <c r="H106">
+        <v>1961</v>
+      </c>
+      <c r="I106">
+        <v>1.4161140000000001</v>
+      </c>
+      <c r="J106">
+        <v>39.328000000000003</v>
+      </c>
+      <c r="K106">
+        <v>160</v>
+      </c>
+      <c r="L106" t="s">
+        <v>30</v>
+      </c>
+      <c r="M106">
+        <v>4916</v>
+      </c>
+      <c r="N106" t="s">
+        <v>97</v>
+      </c>
+      <c r="O106">
+        <v>2777</v>
+      </c>
+      <c r="P106">
+        <v>1770.255672</v>
+      </c>
+      <c r="Q106">
+        <v>125</v>
+      </c>
+      <c r="S106">
+        <v>39.328000000000003</v>
+      </c>
+      <c r="T106">
+        <v>4.5012600000000003</v>
+      </c>
+      <c r="U106">
+        <v>137</v>
+      </c>
+      <c r="V106">
+        <v>4.9333809999999998</v>
+      </c>
+      <c r="W106">
+        <v>35.883212</v>
+      </c>
+      <c r="X106">
+        <v>94</v>
+      </c>
+      <c r="Y106">
+        <v>52.297871999999998</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" t="s">
+        <v>178</v>
+      </c>
+      <c r="D107" t="s">
+        <v>38</v>
+      </c>
+      <c r="E107" t="s">
+        <v>29</v>
+      </c>
+      <c r="F107">
+        <v>150</v>
+      </c>
+      <c r="G107" t="s">
+        <v>39</v>
+      </c>
+      <c r="H107">
+        <v>3624</v>
+      </c>
+      <c r="I107">
+        <v>1.596854</v>
+      </c>
+      <c r="J107">
+        <v>32.893333329999997</v>
+      </c>
+      <c r="K107">
+        <v>160</v>
+      </c>
+      <c r="L107" t="s">
+        <v>30</v>
+      </c>
+      <c r="M107">
+        <v>4934</v>
+      </c>
+      <c r="N107" t="s">
+        <v>97</v>
+      </c>
+      <c r="O107">
+        <v>5787</v>
+      </c>
+      <c r="P107">
+        <v>852.60065699999996</v>
+      </c>
+      <c r="Q107">
+        <v>150</v>
+      </c>
+      <c r="S107">
+        <v>32.893332999999998</v>
+      </c>
+      <c r="T107">
+        <v>2.5920169999999998</v>
+      </c>
+      <c r="U107">
+        <v>176</v>
+      </c>
+      <c r="V107">
+        <v>3.041299</v>
+      </c>
+      <c r="W107">
+        <v>28.034091</v>
+      </c>
+      <c r="X107">
+        <v>140</v>
+      </c>
+      <c r="Y107">
+        <v>35.242857000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
+        <v>179</v>
+      </c>
+      <c r="D108" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" t="s">
+        <v>29</v>
+      </c>
+      <c r="F108">
+        <v>102</v>
+      </c>
+      <c r="G108" t="s">
+        <v>39</v>
+      </c>
+      <c r="H108">
+        <v>3989</v>
+      </c>
+      <c r="I108">
+        <v>1.317874</v>
+      </c>
+      <c r="J108">
+        <v>48.372549020000001</v>
+      </c>
+      <c r="K108">
+        <v>160</v>
+      </c>
+      <c r="L108" t="s">
+        <v>30</v>
+      </c>
+      <c r="M108">
+        <v>4934</v>
+      </c>
+      <c r="N108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O108">
+        <v>5257</v>
+      </c>
+      <c r="P108">
+        <v>938.55811300000005</v>
+      </c>
+      <c r="Q108">
+        <v>102</v>
+      </c>
+      <c r="S108">
+        <v>48.372548999999999</v>
+      </c>
+      <c r="T108">
+        <v>1.9402699999999999</v>
+      </c>
+      <c r="U108">
+        <v>119</v>
+      </c>
+      <c r="V108">
+        <v>2.2636479999999999</v>
+      </c>
+      <c r="W108">
+        <v>41.462184999999998</v>
+      </c>
+      <c r="X108">
+        <v>82</v>
+      </c>
+      <c r="Y108">
+        <v>60.170732000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" t="s">
+        <v>180</v>
+      </c>
+      <c r="D109" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" t="s">
+        <v>29</v>
+      </c>
+      <c r="F109">
+        <v>195</v>
+      </c>
+      <c r="G109" t="s">
+        <v>39</v>
+      </c>
+      <c r="H109">
+        <v>2115</v>
+      </c>
+      <c r="I109">
+        <v>1.6089830000000001</v>
+      </c>
+      <c r="J109">
+        <v>25.261538460000001</v>
+      </c>
+      <c r="K109">
+        <v>160</v>
+      </c>
+      <c r="L109" t="s">
+        <v>30</v>
+      </c>
+      <c r="M109">
+        <v>4926</v>
+      </c>
+      <c r="N109" t="s">
+        <v>181</v>
+      </c>
+      <c r="O109">
+        <v>3403</v>
+      </c>
+      <c r="P109">
+        <v>1447.5462829999999</v>
+      </c>
+      <c r="Q109">
+        <v>195</v>
+      </c>
+      <c r="S109">
+        <v>25.261538000000002</v>
+      </c>
+      <c r="T109">
+        <v>5.7302379999999999</v>
+      </c>
+      <c r="U109">
+        <v>220</v>
+      </c>
+      <c r="V109">
+        <v>6.4648839999999996</v>
+      </c>
+      <c r="W109">
+        <v>22.390909000000001</v>
+      </c>
+      <c r="X109">
+        <v>6</v>
+      </c>
+      <c r="Y109">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" t="s">
+        <v>182</v>
+      </c>
+      <c r="D110" t="s">
+        <v>38</v>
+      </c>
+      <c r="E110" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110">
+        <v>239</v>
+      </c>
+      <c r="G110" t="s">
+        <v>39</v>
+      </c>
+      <c r="H110">
+        <v>3274</v>
+      </c>
+      <c r="I110">
+        <v>1.4602930000000001</v>
+      </c>
+      <c r="J110">
+        <v>20.677824269999999</v>
+      </c>
+      <c r="K110">
+        <v>160</v>
+      </c>
+      <c r="L110" t="s">
+        <v>30</v>
+      </c>
+      <c r="M110">
+        <v>4942</v>
+      </c>
+      <c r="N110" t="s">
+        <v>181</v>
+      </c>
+      <c r="O110">
+        <v>4781</v>
+      </c>
+      <c r="P110">
+        <v>1033.6749629999999</v>
+      </c>
+      <c r="Q110">
+        <v>239</v>
+      </c>
+      <c r="S110">
+        <v>20.677824000000001</v>
+      </c>
+      <c r="T110">
+        <v>4.9989540000000003</v>
+      </c>
+      <c r="U110">
+        <v>265</v>
+      </c>
+      <c r="V110">
+        <v>5.5427730000000004</v>
+      </c>
+      <c r="W110">
+        <v>18.649056999999999</v>
+      </c>
+      <c r="X110">
+        <v>4</v>
+      </c>
+      <c r="Y110">
+        <v>1235.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" t="s">
+        <v>183</v>
+      </c>
+      <c r="D111" t="s">
+        <v>38</v>
+      </c>
+      <c r="E111" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111">
+        <v>148</v>
+      </c>
+      <c r="G111" t="s">
+        <v>39</v>
+      </c>
+      <c r="H111">
+        <v>3815</v>
+      </c>
+      <c r="I111">
+        <v>1.2946260000000001</v>
+      </c>
+      <c r="J111">
+        <v>33.21621622</v>
+      </c>
+      <c r="K111">
+        <v>160</v>
+      </c>
+      <c r="L111" t="s">
+        <v>30</v>
+      </c>
+      <c r="M111">
+        <v>4916</v>
+      </c>
+      <c r="N111" t="s">
+        <v>181</v>
+      </c>
+      <c r="O111">
+        <v>4939</v>
+      </c>
+      <c r="P111">
+        <v>995.34318699999994</v>
+      </c>
+      <c r="Q111">
+        <v>148</v>
+      </c>
+      <c r="S111">
+        <v>33.216216000000003</v>
+      </c>
+      <c r="T111">
+        <v>2.9965579999999998</v>
+      </c>
+      <c r="U111">
+        <v>184</v>
+      </c>
+      <c r="V111">
+        <v>3.7254510000000001</v>
+      </c>
+      <c r="W111">
+        <v>26.717390999999999</v>
+      </c>
+      <c r="X111">
+        <v>23</v>
+      </c>
+      <c r="Y111">
+        <v>213.73912999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>184</v>
+      </c>
+      <c r="D112" t="s">
+        <v>81</v>
+      </c>
+      <c r="E112" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112">
+        <v>90</v>
+      </c>
+      <c r="G112" t="s">
+        <v>39</v>
+      </c>
+      <c r="H112">
+        <v>2749</v>
+      </c>
+      <c r="I112">
+        <v>1.571844</v>
+      </c>
+      <c r="J112">
+        <v>54.9</v>
+      </c>
+      <c r="K112">
+        <v>160</v>
+      </c>
+      <c r="L112" t="s">
+        <v>30</v>
+      </c>
+      <c r="M112">
+        <v>4941</v>
+      </c>
+      <c r="N112" t="s">
+        <v>185</v>
+      </c>
+      <c r="O112">
+        <v>4321</v>
+      </c>
+      <c r="P112">
+        <v>1143.485304</v>
+      </c>
+      <c r="Q112">
+        <v>90</v>
+      </c>
+      <c r="S112">
+        <v>54.9</v>
+      </c>
+      <c r="T112">
+        <v>2.0828509999999998</v>
+      </c>
+      <c r="U112">
+        <v>103</v>
+      </c>
+      <c r="V112">
+        <v>2.3837069999999998</v>
+      </c>
+      <c r="W112">
+        <v>47.970874000000002</v>
+      </c>
+      <c r="X112">
+        <v>70</v>
+      </c>
+      <c r="Y112">
+        <v>70.585713999999996</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>186</v>
+      </c>
+      <c r="D113" t="s">
+        <v>28</v>
+      </c>
+      <c r="E113" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113">
+        <v>86</v>
+      </c>
+      <c r="G113" t="s">
+        <v>39</v>
+      </c>
+      <c r="H113">
+        <v>2228</v>
+      </c>
+      <c r="I113">
+        <v>1.137343</v>
+      </c>
+      <c r="J113">
+        <v>57.418604649999999</v>
+      </c>
+      <c r="K113">
+        <v>160</v>
+      </c>
+      <c r="L113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M113">
+        <v>4938</v>
+      </c>
+      <c r="N113" t="s">
+        <v>114</v>
+      </c>
+      <c r="O113">
+        <v>2534</v>
+      </c>
+      <c r="P113">
+        <v>1948.697711</v>
+      </c>
+      <c r="Q113">
+        <v>86</v>
+      </c>
+      <c r="S113">
+        <v>57.418604999999999</v>
+      </c>
+      <c r="T113">
+        <v>3.3938440000000001</v>
+      </c>
+      <c r="U113">
+        <v>87</v>
+      </c>
+      <c r="V113">
+        <v>3.4333070000000001</v>
+      </c>
+      <c r="W113">
+        <v>56.758620999999998</v>
+      </c>
+      <c r="X113">
+        <v>46</v>
+      </c>
+      <c r="Y113">
+        <v>107.347826</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>187</v>
+      </c>
+      <c r="D114" t="s">
+        <v>38</v>
+      </c>
+      <c r="E114" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114">
+        <v>128</v>
+      </c>
+      <c r="G114" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114">
+        <v>2313</v>
+      </c>
+      <c r="I114">
+        <v>1.7103330000000001</v>
+      </c>
+      <c r="J114">
+        <v>38.390625</v>
+      </c>
+      <c r="K114">
+        <v>160</v>
+      </c>
+      <c r="L114" t="s">
+        <v>30</v>
+      </c>
+      <c r="M114">
+        <v>4914</v>
+      </c>
+      <c r="N114" t="s">
+        <v>107</v>
+      </c>
+      <c r="O114">
+        <v>3956</v>
+      </c>
+      <c r="P114">
+        <v>1242.163802</v>
+      </c>
+      <c r="Q114">
+        <v>128</v>
+      </c>
+      <c r="S114">
+        <v>38.390625</v>
+      </c>
+      <c r="T114">
+        <v>3.235592</v>
+      </c>
+      <c r="U114">
+        <v>166</v>
+      </c>
+      <c r="V114">
+        <v>4.1961579999999996</v>
+      </c>
+      <c r="W114">
+        <v>29.602409999999999</v>
+      </c>
+      <c r="X114">
+        <v>78</v>
+      </c>
+      <c r="Y114">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>25</v>
+      </c>
+      <c r="B115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" t="s">
+        <v>188</v>
+      </c>
+      <c r="D115" t="s">
+        <v>38</v>
+      </c>
+      <c r="E115" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115">
+        <v>232</v>
+      </c>
+      <c r="G115" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115">
+        <v>2839</v>
+      </c>
+      <c r="I115">
+        <v>1.5311729999999999</v>
+      </c>
+      <c r="J115">
+        <v>21.12068966</v>
+      </c>
+      <c r="K115">
+        <v>160</v>
+      </c>
+      <c r="L115" t="s">
+        <v>30</v>
+      </c>
+      <c r="M115">
+        <v>4900</v>
+      </c>
+      <c r="N115" t="s">
+        <v>107</v>
+      </c>
+      <c r="O115">
+        <v>4347</v>
+      </c>
+      <c r="P115">
+        <v>1127.2141710000001</v>
+      </c>
+      <c r="Q115">
+        <v>232</v>
+      </c>
+      <c r="S115">
+        <v>21.12069</v>
+      </c>
+      <c r="T115">
+        <v>5.3370139999999999</v>
+      </c>
+      <c r="U115">
+        <v>254</v>
+      </c>
+      <c r="V115">
+        <v>5.8431100000000002</v>
+      </c>
+      <c r="W115">
+        <v>19.291339000000001</v>
+      </c>
+      <c r="X115">
+        <v>204</v>
+      </c>
+      <c r="Y115">
+        <v>24.019608000000002</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>25</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
+        <v>189</v>
+      </c>
+      <c r="D116" t="s">
+        <v>38</v>
+      </c>
+      <c r="E116" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116">
+        <v>95</v>
+      </c>
+      <c r="G116" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116">
+        <v>3391</v>
+      </c>
+      <c r="I116">
+        <v>1.312297</v>
+      </c>
+      <c r="J116">
+        <v>51.947368419999997</v>
+      </c>
+      <c r="K116">
+        <v>160</v>
+      </c>
+      <c r="L116" t="s">
+        <v>30</v>
+      </c>
+      <c r="M116">
+        <v>4935</v>
+      </c>
+      <c r="N116" t="s">
+        <v>107</v>
+      </c>
+      <c r="O116">
+        <v>4450</v>
+      </c>
+      <c r="P116">
+        <v>1108.9887639999999</v>
+      </c>
+      <c r="Q116">
+        <v>95</v>
+      </c>
+      <c r="S116">
+        <v>51.947367999999997</v>
+      </c>
+      <c r="T116">
+        <v>2.1348310000000001</v>
+      </c>
+      <c r="U116">
+        <v>104</v>
+      </c>
+      <c r="V116">
+        <v>2.3370790000000001</v>
+      </c>
+      <c r="W116">
+        <v>47.451923000000001</v>
+      </c>
+      <c r="X116">
+        <v>80</v>
+      </c>
+      <c r="Y116">
+        <v>61.6875</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>25</v>
+      </c>
+      <c r="B117" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" t="s">
+        <v>190</v>
+      </c>
+      <c r="D117" t="s">
+        <v>38</v>
+      </c>
+      <c r="E117" t="s">
+        <v>29</v>
+      </c>
+      <c r="F117">
+        <v>255</v>
+      </c>
+      <c r="G117" t="s">
+        <v>39</v>
+      </c>
+      <c r="H117">
+        <v>3376</v>
+      </c>
+      <c r="I117">
+        <v>1.409656</v>
+      </c>
+      <c r="J117">
+        <v>19.403921570000001</v>
+      </c>
+      <c r="K117">
+        <v>160</v>
+      </c>
+      <c r="L117" t="s">
+        <v>30</v>
+      </c>
+      <c r="M117">
+        <v>4948</v>
+      </c>
+      <c r="N117" t="s">
+        <v>107</v>
+      </c>
+      <c r="O117">
+        <v>4759</v>
+      </c>
+      <c r="P117">
+        <v>1039.7142260000001</v>
+      </c>
+      <c r="Q117">
+        <v>255</v>
+      </c>
+      <c r="S117">
+        <v>19.403922000000001</v>
+      </c>
+      <c r="T117">
+        <v>5.3582689999999999</v>
+      </c>
+      <c r="U117">
+        <v>289</v>
+      </c>
+      <c r="V117">
+        <v>6.0727039999999999</v>
+      </c>
+      <c r="W117">
+        <v>17.121106999999999</v>
+      </c>
+      <c r="X117">
+        <v>6</v>
+      </c>
+      <c r="Y117">
+        <v>824.66666699999996</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>25</v>
+      </c>
+      <c r="B118" t="s">
+        <v>26</v>
+      </c>
+      <c r="C118" t="s">
+        <v>191</v>
+      </c>
+      <c r="D118" t="s">
+        <v>38</v>
+      </c>
+      <c r="E118" t="s">
+        <v>29</v>
+      </c>
+      <c r="F118">
+        <v>135</v>
+      </c>
+      <c r="G118" t="s">
+        <v>39</v>
+      </c>
+      <c r="H118">
+        <v>3041</v>
+      </c>
+      <c r="I118">
+        <v>1.3765210000000001</v>
+      </c>
+      <c r="J118">
+        <v>36.481481479999999</v>
+      </c>
+      <c r="K118">
+        <v>160</v>
+      </c>
+      <c r="L118" t="s">
+        <v>30</v>
+      </c>
+      <c r="M118">
+        <v>4925</v>
+      </c>
+      <c r="N118" t="s">
+        <v>107</v>
+      </c>
+      <c r="O118">
+        <v>4186</v>
+      </c>
+      <c r="P118">
+        <v>1176.5408500000001</v>
+      </c>
+      <c r="Q118">
+        <v>135</v>
+      </c>
+      <c r="S118">
+        <v>36.481481000000002</v>
+      </c>
+      <c r="T118">
+        <v>3.2250359999999998</v>
+      </c>
+      <c r="U118">
+        <v>144</v>
+      </c>
+      <c r="V118">
+        <v>3.4400379999999999</v>
+      </c>
+      <c r="W118">
+        <v>34.201388999999999</v>
+      </c>
+      <c r="X118">
+        <v>121</v>
+      </c>
+      <c r="Y118">
+        <v>40.702478999999997</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>25</v>
+      </c>
+      <c r="B119" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" t="s">
+        <v>192</v>
+      </c>
+      <c r="D119" t="s">
+        <v>38</v>
+      </c>
+      <c r="E119" t="s">
+        <v>29</v>
+      </c>
+      <c r="F119">
+        <v>159</v>
+      </c>
+      <c r="G119" t="s">
+        <v>39</v>
+      </c>
+      <c r="H119">
+        <v>3887</v>
+      </c>
+      <c r="I119">
+        <v>1.53769</v>
+      </c>
+      <c r="J119">
+        <v>30.937106920000002</v>
+      </c>
+      <c r="K119">
+        <v>160</v>
+      </c>
+      <c r="L119" t="s">
+        <v>30</v>
+      </c>
+      <c r="M119">
+        <v>4919</v>
+      </c>
+      <c r="N119" t="s">
+        <v>107</v>
+      </c>
+      <c r="O119">
+        <v>5977</v>
+      </c>
+      <c r="P119">
+        <v>822.98812099999998</v>
+      </c>
+      <c r="Q119">
+        <v>159</v>
+      </c>
+      <c r="S119">
+        <v>30.937107000000001</v>
+      </c>
+      <c r="T119">
+        <v>2.6601970000000001</v>
+      </c>
+      <c r="U119">
+        <v>202</v>
+      </c>
+      <c r="V119">
+        <v>3.3796219999999999</v>
+      </c>
+      <c r="W119">
+        <v>24.351485</v>
+      </c>
+      <c r="X119">
+        <v>14</v>
+      </c>
+      <c r="Y119">
+        <v>351.35714300000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" t="s">
+        <v>26</v>
+      </c>
+      <c r="C120" t="s">
+        <v>193</v>
+      </c>
+      <c r="D120" t="s">
+        <v>38</v>
+      </c>
+      <c r="E120" t="s">
+        <v>29</v>
+      </c>
+      <c r="F120">
+        <v>127</v>
+      </c>
+      <c r="G120" t="s">
+        <v>39</v>
+      </c>
+      <c r="H120">
+        <v>3319</v>
+      </c>
+      <c r="I120">
+        <v>1.49081</v>
+      </c>
+      <c r="J120">
+        <v>38.95275591</v>
+      </c>
+      <c r="K120">
+        <v>160</v>
+      </c>
+      <c r="L120" t="s">
+        <v>30</v>
+      </c>
+      <c r="M120">
+        <v>4947</v>
+      </c>
+      <c r="N120" t="s">
+        <v>107</v>
+      </c>
+      <c r="O120">
+        <v>4948</v>
+      </c>
+      <c r="P120">
+        <v>999.79789800000003</v>
+      </c>
+      <c r="Q120">
+        <v>127</v>
+      </c>
+      <c r="S120">
+        <v>38.952756000000001</v>
+      </c>
+      <c r="T120">
+        <v>2.566694</v>
+      </c>
+      <c r="U120">
+        <v>159</v>
+      </c>
+      <c r="V120">
+        <v>3.2134200000000002</v>
+      </c>
+      <c r="W120">
+        <v>31.113208</v>
+      </c>
+      <c r="X120">
+        <v>91</v>
+      </c>
+      <c r="Y120">
+        <v>54.362636999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>194</v>
+      </c>
+      <c r="D121" t="s">
+        <v>38</v>
+      </c>
+      <c r="E121" t="s">
+        <v>29</v>
+      </c>
+      <c r="F121">
+        <v>81</v>
+      </c>
+      <c r="G121" t="s">
+        <v>39</v>
+      </c>
+      <c r="H121">
+        <v>2563</v>
+      </c>
+      <c r="I121">
+        <v>1.5005850000000001</v>
+      </c>
+      <c r="J121">
+        <v>61.049382719999997</v>
+      </c>
+      <c r="K121">
+        <v>160</v>
+      </c>
+      <c r="L121" t="s">
+        <v>30</v>
+      </c>
+      <c r="M121">
+        <v>4945</v>
+      </c>
+      <c r="N121" t="s">
+        <v>107</v>
+      </c>
+      <c r="O121">
+        <v>3846</v>
+      </c>
+      <c r="P121">
+        <v>1285.75143</v>
+      </c>
+      <c r="Q121">
+        <v>81</v>
+      </c>
+      <c r="S121">
+        <v>61.049382999999999</v>
+      </c>
+      <c r="T121">
+        <v>2.1060840000000001</v>
+      </c>
+      <c r="U121">
+        <v>100</v>
+      </c>
+      <c r="V121">
+        <v>2.600104</v>
+      </c>
+      <c r="W121">
+        <v>49.45</v>
+      </c>
+      <c r="X121">
+        <v>68</v>
+      </c>
+      <c r="Y121">
+        <v>72.720588000000006</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>25</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>195</v>
+      </c>
+      <c r="D122" t="s">
+        <v>38</v>
+      </c>
+      <c r="E122" t="s">
+        <v>29</v>
+      </c>
+      <c r="F122">
+        <v>75</v>
+      </c>
+      <c r="G122" t="s">
+        <v>39</v>
+      </c>
+      <c r="H122">
+        <v>3802</v>
+      </c>
+      <c r="I122">
+        <v>1.643346</v>
+      </c>
+      <c r="J122">
+        <v>66.08</v>
+      </c>
+      <c r="K122">
+        <v>160</v>
+      </c>
+      <c r="L122" t="s">
+        <v>30</v>
+      </c>
+      <c r="M122">
+        <v>4956</v>
+      </c>
+      <c r="N122" t="s">
+        <v>107</v>
+      </c>
+      <c r="O122">
+        <v>6248</v>
+      </c>
+      <c r="P122">
+        <v>793.21382800000003</v>
+      </c>
+      <c r="Q122">
+        <v>75</v>
+      </c>
+      <c r="S122">
+        <v>66.08</v>
+      </c>
+      <c r="T122">
+        <v>1.2003839999999999</v>
+      </c>
+      <c r="U122">
+        <v>79</v>
+      </c>
+      <c r="V122">
+        <v>1.264405</v>
+      </c>
+      <c r="W122">
+        <v>62.734177000000003</v>
+      </c>
+      <c r="X122">
+        <v>56</v>
+      </c>
+      <c r="Y122">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>196</v>
+      </c>
+      <c r="D123" t="s">
+        <v>38</v>
+      </c>
+      <c r="E123" t="s">
+        <v>29</v>
+      </c>
+      <c r="F123">
+        <v>184</v>
+      </c>
+      <c r="G123" t="s">
+        <v>39</v>
+      </c>
+      <c r="H123">
+        <v>2984</v>
+      </c>
+      <c r="I123">
+        <v>1.418566</v>
+      </c>
+      <c r="J123">
+        <v>26.733695650000001</v>
+      </c>
+      <c r="K123">
+        <v>160</v>
+      </c>
+      <c r="L123" t="s">
+        <v>30</v>
+      </c>
+      <c r="M123">
+        <v>4919</v>
+      </c>
+      <c r="N123" t="s">
+        <v>107</v>
+      </c>
+      <c r="O123">
+        <v>4233</v>
+      </c>
+      <c r="P123">
+        <v>1162.060005</v>
+      </c>
+      <c r="Q123">
+        <v>184</v>
+      </c>
+      <c r="S123">
+        <v>26.733695999999998</v>
+      </c>
+      <c r="T123">
+        <v>4.3467989999999999</v>
+      </c>
+      <c r="U123">
+        <v>225</v>
+      </c>
+      <c r="V123">
+        <v>5.3153790000000001</v>
+      </c>
+      <c r="W123">
+        <v>21.862221999999999</v>
+      </c>
+      <c r="X123">
+        <v>166</v>
+      </c>
+      <c r="Y123">
+        <v>29.632529999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
+        <v>197</v>
+      </c>
+      <c r="D124" t="s">
+        <v>38</v>
+      </c>
+      <c r="E124" t="s">
+        <v>29</v>
+      </c>
+      <c r="F124">
+        <v>217</v>
+      </c>
+      <c r="G124" t="s">
+        <v>39</v>
+      </c>
+      <c r="H124">
+        <v>4969</v>
+      </c>
+      <c r="I124">
+        <v>1.4073249999999999</v>
+      </c>
+      <c r="J124">
+        <v>22.82949309</v>
+      </c>
+      <c r="K124">
+        <v>160</v>
+      </c>
+      <c r="L124" t="s">
+        <v>30</v>
+      </c>
+      <c r="M124">
+        <v>4954</v>
+      </c>
+      <c r="N124" t="s">
+        <v>107</v>
+      </c>
+      <c r="O124">
+        <v>6993</v>
+      </c>
+      <c r="P124">
+        <v>708.42270799999994</v>
+      </c>
+      <c r="Q124">
+        <v>217</v>
+      </c>
+      <c r="S124">
+        <v>22.829492999999999</v>
+      </c>
+      <c r="T124">
+        <v>3.1031029999999999</v>
+      </c>
+      <c r="U124">
+        <v>279</v>
+      </c>
+      <c r="V124">
+        <v>3.9897040000000001</v>
+      </c>
+      <c r="W124">
+        <v>17.756271999999999</v>
+      </c>
+      <c r="X124">
+        <v>182</v>
+      </c>
+      <c r="Y124">
+        <v>27.21978</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" t="s">
+        <v>198</v>
+      </c>
+      <c r="D125" t="s">
+        <v>38</v>
+      </c>
+      <c r="E125" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125">
+        <v>245</v>
+      </c>
+      <c r="G125" t="s">
+        <v>39</v>
+      </c>
+      <c r="H125">
+        <v>3466</v>
+      </c>
+      <c r="I125">
+        <v>1.3366990000000001</v>
+      </c>
+      <c r="J125">
+        <v>20</v>
+      </c>
+      <c r="K125">
+        <v>160</v>
+      </c>
+      <c r="L125" t="s">
+        <v>30</v>
+      </c>
+      <c r="M125">
+        <v>4900</v>
+      </c>
+      <c r="N125" t="s">
+        <v>107</v>
+      </c>
+      <c r="O125">
+        <v>4633</v>
+      </c>
+      <c r="P125">
+        <v>1057.6300450000001</v>
+      </c>
+      <c r="Q125">
+        <v>245</v>
+      </c>
+      <c r="S125">
+        <v>20</v>
+      </c>
+      <c r="T125">
+        <v>5.2881499999999999</v>
+      </c>
+      <c r="U125">
+        <v>289</v>
+      </c>
+      <c r="V125">
+        <v>6.2378590000000003</v>
+      </c>
+      <c r="W125">
+        <v>16.955017000000002</v>
+      </c>
+      <c r="X125">
+        <v>220</v>
+      </c>
+      <c r="Y125">
+        <v>22.272727</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>199</v>
+      </c>
+      <c r="D126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E126" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126">
+        <v>446</v>
+      </c>
+      <c r="G126" t="s">
+        <v>39</v>
+      </c>
+      <c r="H126">
+        <v>3907</v>
+      </c>
+      <c r="I126">
+        <v>1.37676</v>
+      </c>
+      <c r="J126">
+        <v>11.03811659</v>
+      </c>
+      <c r="K126">
+        <v>160</v>
+      </c>
+      <c r="L126" t="s">
+        <v>30</v>
+      </c>
+      <c r="M126">
+        <v>4923</v>
+      </c>
+      <c r="N126" t="s">
+        <v>107</v>
+      </c>
+      <c r="O126">
+        <v>5379</v>
+      </c>
+      <c r="P126">
+        <v>915.22587799999997</v>
+      </c>
+      <c r="Q126">
+        <v>446</v>
+      </c>
+      <c r="S126">
+        <v>11.038117</v>
+      </c>
+      <c r="T126">
+        <v>8.2915039999999998</v>
+      </c>
+      <c r="U126">
+        <v>499</v>
+      </c>
+      <c r="V126">
+        <v>9.2768169999999994</v>
+      </c>
+      <c r="W126">
+        <v>9.8657310000000003</v>
+      </c>
+      <c r="X126">
+        <v>397</v>
+      </c>
+      <c r="Y126">
+        <v>12.400504</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>200</v>
+      </c>
+      <c r="D127" t="s">
+        <v>38</v>
+      </c>
+      <c r="E127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127">
+        <v>560</v>
+      </c>
+      <c r="G127" t="s">
+        <v>39</v>
+      </c>
+      <c r="H127">
+        <v>5382</v>
+      </c>
+      <c r="I127">
+        <v>1.3290599999999999</v>
+      </c>
+      <c r="J127">
+        <v>8.8357142900000003</v>
+      </c>
+      <c r="K127">
+        <v>160</v>
+      </c>
+      <c r="L127" t="s">
+        <v>30</v>
+      </c>
+      <c r="M127">
+        <v>4948</v>
+      </c>
+      <c r="N127" t="s">
+        <v>107</v>
+      </c>
+      <c r="O127">
+        <v>7153</v>
+      </c>
+      <c r="P127">
+        <v>691.73773200000005</v>
+      </c>
+      <c r="Q127">
+        <v>560</v>
+      </c>
+      <c r="S127">
+        <v>8.8357139999999994</v>
+      </c>
+      <c r="T127">
+        <v>7.8288830000000003</v>
+      </c>
+      <c r="U127">
+        <v>643</v>
+      </c>
+      <c r="V127">
+        <v>8.9892350000000008</v>
+      </c>
+      <c r="W127">
+        <v>7.6951790000000004</v>
+      </c>
+      <c r="X127">
+        <v>465</v>
+      </c>
+      <c r="Y127">
+        <v>10.64086</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>25</v>
+      </c>
+      <c r="B128" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" t="s">
+        <v>201</v>
+      </c>
+      <c r="D128" t="s">
+        <v>38</v>
+      </c>
+      <c r="E128" t="s">
+        <v>29</v>
+      </c>
+      <c r="F128">
+        <v>190</v>
+      </c>
+      <c r="G128" t="s">
+        <v>39</v>
+      </c>
+      <c r="H128">
+        <v>3455</v>
+      </c>
+      <c r="I128">
+        <v>1.4749639999999999</v>
+      </c>
+      <c r="J128">
+        <v>25.94736842</v>
+      </c>
+      <c r="K128">
+        <v>160</v>
+      </c>
+      <c r="L128" t="s">
+        <v>30</v>
+      </c>
+      <c r="M128">
+        <v>4930</v>
+      </c>
+      <c r="N128" t="s">
+        <v>107</v>
+      </c>
+      <c r="O128">
+        <v>5096</v>
+      </c>
+      <c r="P128">
+        <v>967.425432</v>
+      </c>
+      <c r="Q128">
+        <v>190</v>
+      </c>
+      <c r="S128">
+        <v>25.947368000000001</v>
+      </c>
+      <c r="T128">
+        <v>3.7284139999999999</v>
+      </c>
+      <c r="U128">
+        <v>225</v>
+      </c>
+      <c r="V128">
+        <v>4.4152279999999999</v>
+      </c>
+      <c r="W128">
+        <v>21.911110999999998</v>
+      </c>
+      <c r="X128">
+        <v>167</v>
+      </c>
+      <c r="Y128">
+        <v>29.520958</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" t="s">
+        <v>202</v>
+      </c>
+      <c r="D129" t="s">
+        <v>38</v>
+      </c>
+      <c r="E129" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129">
+        <v>183</v>
+      </c>
+      <c r="G129" t="s">
+        <v>39</v>
+      </c>
+      <c r="H129">
+        <v>3090</v>
+      </c>
+      <c r="I129">
+        <v>1.538511</v>
+      </c>
+      <c r="J129">
+        <v>26.994535519999999</v>
+      </c>
+      <c r="K129">
+        <v>160</v>
+      </c>
+      <c r="L129" t="s">
+        <v>30</v>
+      </c>
+      <c r="M129">
+        <v>4940</v>
+      </c>
+      <c r="N129" t="s">
+        <v>107</v>
+      </c>
+      <c r="O129">
+        <v>4754</v>
+      </c>
+      <c r="P129">
+        <v>1039.124947</v>
+      </c>
+      <c r="Q129">
+        <v>183</v>
+      </c>
+      <c r="S129">
+        <v>26.994536</v>
+      </c>
+      <c r="T129">
+        <v>3.8493900000000001</v>
+      </c>
+      <c r="U129">
+        <v>224</v>
+      </c>
+      <c r="V129">
+        <v>4.7118219999999997</v>
+      </c>
+      <c r="W129">
+        <v>22.053571000000002</v>
+      </c>
+      <c r="X129">
+        <v>162</v>
+      </c>
+      <c r="Y129">
+        <v>30.493827</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>203</v>
+      </c>
+      <c r="D130" t="s">
+        <v>38</v>
+      </c>
+      <c r="E130" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130">
+        <v>185</v>
+      </c>
+      <c r="G130" t="s">
+        <v>39</v>
+      </c>
+      <c r="H130">
+        <v>4478</v>
+      </c>
+      <c r="I130">
+        <v>1.2728900000000001</v>
+      </c>
+      <c r="J130">
+        <v>26.681081079999998</v>
+      </c>
+      <c r="K130">
+        <v>160</v>
+      </c>
+      <c r="L130" t="s">
+        <v>30</v>
+      </c>
+      <c r="M130">
+        <v>4936</v>
+      </c>
+      <c r="N130" t="s">
+        <v>107</v>
+      </c>
+      <c r="O130">
+        <v>5700</v>
+      </c>
+      <c r="P130">
+        <v>865.96491200000003</v>
+      </c>
+      <c r="Q130">
+        <v>185</v>
+      </c>
+      <c r="S130">
+        <v>26.681080999999999</v>
+      </c>
+      <c r="T130">
+        <v>3.2456140000000002</v>
+      </c>
+      <c r="U130">
+        <v>213</v>
+      </c>
+      <c r="V130">
+        <v>3.7368420000000002</v>
+      </c>
+      <c r="W130">
+        <v>23.173708999999999</v>
+      </c>
+      <c r="X130">
+        <v>150</v>
+      </c>
+      <c r="Y130">
+        <v>32.906666999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" t="s">
+        <v>204</v>
+      </c>
+      <c r="D131" t="s">
+        <v>38</v>
+      </c>
+      <c r="E131" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131">
+        <v>59</v>
+      </c>
+      <c r="G131" t="s">
+        <v>39</v>
+      </c>
+      <c r="H131">
+        <v>3216</v>
+      </c>
+      <c r="I131">
+        <v>1.648943</v>
+      </c>
+      <c r="J131">
+        <v>83.203389830000006</v>
+      </c>
+      <c r="K131">
+        <v>160</v>
+      </c>
+      <c r="L131" t="s">
+        <v>30</v>
+      </c>
+      <c r="M131">
+        <v>4909</v>
+      </c>
+      <c r="N131" t="s">
+        <v>107</v>
+      </c>
+      <c r="O131">
+        <v>5303</v>
+      </c>
+      <c r="P131">
+        <v>925.70243300000004</v>
+      </c>
+      <c r="Q131">
+        <v>59</v>
+      </c>
+      <c r="S131">
+        <v>83.203389999999999</v>
+      </c>
+      <c r="T131">
+        <v>1.1125780000000001</v>
+      </c>
+      <c r="U131">
+        <v>95</v>
+      </c>
+      <c r="V131">
+        <v>1.791439</v>
+      </c>
+      <c r="W131">
+        <v>51.673684000000002</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" t="s">
+        <v>205</v>
+      </c>
+      <c r="D132" t="s">
+        <v>38</v>
+      </c>
+      <c r="E132" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132">
+        <v>122</v>
+      </c>
+      <c r="G132" t="s">
+        <v>39</v>
+      </c>
+      <c r="H132">
+        <v>3386</v>
+      </c>
+      <c r="I132">
+        <v>1.232132</v>
+      </c>
+      <c r="J132">
+        <v>40.491803279999999</v>
+      </c>
+      <c r="K132">
+        <v>160</v>
+      </c>
+      <c r="L132" t="s">
+        <v>30</v>
+      </c>
+      <c r="M132">
+        <v>4940</v>
+      </c>
+      <c r="N132" t="s">
+        <v>107</v>
+      </c>
+      <c r="O132">
+        <v>4172</v>
+      </c>
+      <c r="P132">
+        <v>1184.084372</v>
+      </c>
+      <c r="Q132">
+        <v>122</v>
+      </c>
+      <c r="S132">
+        <v>40.491802999999997</v>
+      </c>
+      <c r="T132">
+        <v>2.9242569999999999</v>
+      </c>
+      <c r="U132">
+        <v>129</v>
+      </c>
+      <c r="V132">
+        <v>3.0920420000000002</v>
+      </c>
+      <c r="W132">
+        <v>38.294573999999997</v>
+      </c>
+      <c r="X132">
+        <v>96</v>
+      </c>
+      <c r="Y132">
+        <v>51.458333000000003</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>25</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" t="s">
+        <v>186</v>
+      </c>
+      <c r="D133" t="s">
+        <v>28</v>
+      </c>
+      <c r="E133" t="s">
+        <v>29</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>160</v>
+      </c>
+      <c r="L133" t="s">
+        <v>30</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133" t="s">
+        <v>114</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="U133">
+        <v>0</v>
+      </c>
+      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>25</v>
+      </c>
+      <c r="B134" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" t="s">
+        <v>206</v>
+      </c>
+      <c r="D134" t="s">
+        <v>38</v>
+      </c>
+      <c r="E134" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134">
+        <v>141</v>
+      </c>
+      <c r="G134" t="s">
+        <v>39</v>
+      </c>
+      <c r="H134">
+        <v>4150</v>
+      </c>
+      <c r="I134">
+        <v>1.180482</v>
+      </c>
+      <c r="J134">
+        <v>34.836879430000003</v>
+      </c>
+      <c r="K134">
+        <v>160</v>
+      </c>
+      <c r="L134" t="s">
+        <v>30</v>
+      </c>
+      <c r="M134">
+        <v>4912</v>
+      </c>
+      <c r="N134" t="s">
+        <v>107</v>
+      </c>
+      <c r="O134">
+        <v>4899</v>
+      </c>
+      <c r="P134">
+        <v>1002.653603</v>
+      </c>
+      <c r="Q134">
+        <v>141</v>
+      </c>
+      <c r="S134">
+        <v>34.836879000000003</v>
+      </c>
+      <c r="T134">
+        <v>2.8781379999999999</v>
+      </c>
+      <c r="U134">
+        <v>159</v>
+      </c>
+      <c r="V134">
+        <v>3.2455599999999998</v>
+      </c>
+      <c r="W134">
+        <v>30.893082</v>
+      </c>
+      <c r="X134">
+        <v>113</v>
+      </c>
+      <c r="Y134">
+        <v>43.469026999999997</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>25</v>
+      </c>
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" t="s">
+        <v>207</v>
+      </c>
+      <c r="D135" t="s">
+        <v>38</v>
+      </c>
+      <c r="E135" t="s">
+        <v>29</v>
+      </c>
+      <c r="F135">
+        <v>207</v>
+      </c>
+      <c r="G135" t="s">
+        <v>39</v>
+      </c>
+      <c r="H135">
+        <v>2893</v>
+      </c>
+      <c r="I135">
+        <v>1.3681300000000001</v>
+      </c>
+      <c r="J135">
+        <v>23.83091787</v>
+      </c>
+      <c r="K135">
+        <v>160</v>
+      </c>
+      <c r="L135" t="s">
+        <v>30</v>
+      </c>
+      <c r="M135">
+        <v>4933</v>
+      </c>
+      <c r="N135" t="s">
+        <v>107</v>
+      </c>
+      <c r="O135">
+        <v>3958</v>
+      </c>
+      <c r="P135">
+        <v>1246.336534</v>
+      </c>
+      <c r="Q135">
+        <v>207</v>
+      </c>
+      <c r="S135">
+        <v>23.830918</v>
+      </c>
+      <c r="T135">
+        <v>5.229914</v>
+      </c>
+      <c r="U135">
+        <v>233</v>
+      </c>
+      <c r="V135">
+        <v>5.8868119999999999</v>
+      </c>
+      <c r="W135">
+        <v>21.171673999999999</v>
+      </c>
+      <c r="X135">
+        <v>8</v>
+      </c>
+      <c r="Y135">
+        <v>616.625</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" t="s">
+        <v>208</v>
+      </c>
+      <c r="D136" t="s">
+        <v>38</v>
+      </c>
+      <c r="E136" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136">
+        <v>184</v>
+      </c>
+      <c r="G136" t="s">
+        <v>39</v>
+      </c>
+      <c r="H136">
+        <v>5273</v>
+      </c>
+      <c r="I136">
+        <v>1.1907829999999999</v>
+      </c>
+      <c r="J136">
+        <v>26.858695650000001</v>
+      </c>
+      <c r="K136">
+        <v>160</v>
+      </c>
+      <c r="L136" t="s">
+        <v>30</v>
+      </c>
+      <c r="M136">
+        <v>4942</v>
+      </c>
+      <c r="N136" t="s">
+        <v>107</v>
+      </c>
+      <c r="O136">
+        <v>6279</v>
+      </c>
+      <c r="P136">
+        <v>787.06800399999997</v>
+      </c>
+      <c r="Q136">
+        <v>184</v>
+      </c>
+      <c r="S136">
+        <v>26.858695999999998</v>
+      </c>
+      <c r="T136">
+        <v>2.9304030000000001</v>
+      </c>
+      <c r="U136">
+        <v>216</v>
+      </c>
+      <c r="V136">
+        <v>3.4400379999999999</v>
+      </c>
+      <c r="W136">
+        <v>22.879629999999999</v>
+      </c>
+      <c r="X136">
+        <v>165</v>
+      </c>
+      <c r="Y136">
+        <v>29.951515000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" t="s">
+        <v>209</v>
+      </c>
+      <c r="D137" t="s">
+        <v>38</v>
+      </c>
+      <c r="E137" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137">
+        <v>235</v>
+      </c>
+      <c r="G137" t="s">
+        <v>39</v>
+      </c>
+      <c r="H137">
+        <v>6121</v>
+      </c>
+      <c r="I137">
+        <v>1.2579640000000001</v>
+      </c>
+      <c r="J137">
+        <v>20.991489359999999</v>
+      </c>
+      <c r="K137">
+        <v>160</v>
+      </c>
+      <c r="L137" t="s">
+        <v>30</v>
+      </c>
+      <c r="M137">
+        <v>4933</v>
+      </c>
+      <c r="N137" t="s">
+        <v>107</v>
+      </c>
+      <c r="O137">
+        <v>7700</v>
+      </c>
+      <c r="P137">
+        <v>640.64935100000002</v>
+      </c>
+      <c r="Q137">
+        <v>235</v>
+      </c>
+      <c r="S137">
+        <v>20.991489000000001</v>
+      </c>
+      <c r="T137">
+        <v>3.0519479999999999</v>
+      </c>
+      <c r="U137">
+        <v>278</v>
+      </c>
+      <c r="V137">
+        <v>3.6103900000000002</v>
+      </c>
+      <c r="W137">
+        <v>17.744603999999999</v>
+      </c>
+      <c r="X137">
+        <v>192</v>
+      </c>
+      <c r="Y137">
+        <v>25.692708</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>25</v>
+      </c>
+      <c r="B138" t="s">
+        <v>26</v>
+      </c>
+      <c r="C138" t="s">
+        <v>210</v>
+      </c>
+      <c r="D138" t="s">
+        <v>38</v>
+      </c>
+      <c r="E138" t="s">
+        <v>29</v>
+      </c>
+      <c r="F138">
+        <v>162</v>
+      </c>
+      <c r="G138" t="s">
+        <v>39</v>
+      </c>
+      <c r="H138">
+        <v>6032</v>
+      </c>
+      <c r="I138">
+        <v>1.3071950000000001</v>
+      </c>
+      <c r="J138">
+        <v>30.43209877</v>
+      </c>
+      <c r="K138">
+        <v>160</v>
+      </c>
+      <c r="L138" t="s">
+        <v>30</v>
+      </c>
+      <c r="M138">
+        <v>4930</v>
+      </c>
+      <c r="N138" t="s">
+        <v>107</v>
+      </c>
+      <c r="O138">
+        <v>7885</v>
+      </c>
+      <c r="P138">
+        <v>625.23779300000001</v>
+      </c>
+      <c r="Q138">
+        <v>162</v>
+      </c>
+      <c r="S138">
+        <v>30.432099000000001</v>
+      </c>
+      <c r="T138">
+        <v>2.0545339999999999</v>
+      </c>
+      <c r="U138">
+        <v>226</v>
+      </c>
+      <c r="V138">
+        <v>2.8662019999999999</v>
+      </c>
+      <c r="W138">
+        <v>21.814159</v>
+      </c>
+      <c r="X138">
+        <v>148</v>
+      </c>
+      <c r="Y138">
+        <v>33.310811000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" t="s">
+        <v>211</v>
+      </c>
+      <c r="D139" t="s">
+        <v>28</v>
+      </c>
+      <c r="E139" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139">
+        <v>21</v>
+      </c>
+      <c r="G139" t="s">
+        <v>39</v>
+      </c>
+      <c r="H139">
+        <v>914</v>
+      </c>
+      <c r="I139">
+        <v>1.131291</v>
+      </c>
+      <c r="J139">
+        <v>75.761904759999993</v>
+      </c>
+      <c r="K139">
+        <v>160</v>
+      </c>
+      <c r="L139" t="s">
+        <v>30</v>
+      </c>
+      <c r="M139">
+        <v>1591</v>
+      </c>
+      <c r="N139" t="s">
+        <v>212</v>
+      </c>
+      <c r="O139">
+        <v>1034</v>
+      </c>
+      <c r="P139">
+        <v>1538.68472</v>
+      </c>
+      <c r="Q139">
+        <v>21</v>
+      </c>
+      <c r="S139">
+        <v>75.761904999999999</v>
+      </c>
+      <c r="T139">
+        <v>2.030948</v>
+      </c>
+      <c r="U139">
+        <v>22</v>
+      </c>
+      <c r="V139">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="W139">
+        <v>72.318181999999993</v>
+      </c>
+      <c r="X139">
+        <v>11</v>
+      </c>
+      <c r="Y139">
+        <v>144.63636399999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>25</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" t="s">
+        <v>213</v>
+      </c>
+      <c r="D140" t="s">
+        <v>38</v>
+      </c>
+      <c r="E140" t="s">
+        <v>29</v>
+      </c>
+      <c r="F140">
+        <v>71</v>
+      </c>
+      <c r="G140" t="s">
+        <v>39</v>
+      </c>
+      <c r="H140">
+        <v>2137</v>
+      </c>
+      <c r="I140">
+        <v>1.052878</v>
+      </c>
+      <c r="J140">
+        <v>68.577464789999993</v>
+      </c>
+      <c r="K140">
+        <v>160</v>
+      </c>
+      <c r="L140" t="s">
+        <v>30</v>
+      </c>
+      <c r="M140">
+        <v>4869</v>
+      </c>
+      <c r="N140" t="s">
+        <v>63</v>
+      </c>
+      <c r="O140">
+        <v>2250</v>
+      </c>
+      <c r="P140">
+        <v>2164</v>
+      </c>
+      <c r="Q140">
+        <v>71</v>
+      </c>
+      <c r="S140">
+        <v>68.577465000000004</v>
+      </c>
+      <c r="T140">
+        <v>3.1555559999999998</v>
+      </c>
+      <c r="U140">
+        <v>71</v>
+      </c>
+      <c r="V140">
+        <v>3.1555559999999998</v>
+      </c>
+      <c r="W140">
+        <v>68.577465000000004</v>
+      </c>
+      <c r="X140">
+        <v>29</v>
+      </c>
+      <c r="Y140">
+        <v>167.89655200000001</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141" t="s">
+        <v>26</v>
+      </c>
+      <c r="C141" t="s">
+        <v>214</v>
+      </c>
+      <c r="D141" t="s">
+        <v>38</v>
+      </c>
+      <c r="E141" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141">
+        <v>75</v>
+      </c>
+      <c r="G141" t="s">
+        <v>39</v>
+      </c>
+      <c r="H141">
+        <v>3579</v>
+      </c>
+      <c r="I141">
+        <v>1.052249</v>
+      </c>
+      <c r="J141">
+        <v>65.426666670000003</v>
+      </c>
+      <c r="K141">
+        <v>160</v>
+      </c>
+      <c r="L141" t="s">
+        <v>30</v>
+      </c>
+      <c r="M141">
+        <v>4907</v>
+      </c>
+      <c r="N141" t="s">
+        <v>63</v>
+      </c>
+      <c r="O141">
+        <v>3766</v>
+      </c>
+      <c r="P141">
+        <v>1302.973978</v>
+      </c>
+      <c r="Q141">
+        <v>75</v>
+      </c>
+      <c r="S141">
+        <v>65.426666999999995</v>
+      </c>
+      <c r="T141">
+        <v>1.991503</v>
+      </c>
+      <c r="U141">
+        <v>81</v>
+      </c>
+      <c r="V141">
+        <v>2.1508229999999999</v>
+      </c>
+      <c r="W141">
+        <v>60.580247</v>
+      </c>
+      <c r="X141">
+        <v>26</v>
+      </c>
+      <c r="Y141">
+        <v>188.73076900000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>25</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" t="s">
+        <v>215</v>
+      </c>
+      <c r="D142" t="s">
+        <v>38</v>
+      </c>
+      <c r="E142" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142">
+        <v>103</v>
+      </c>
+      <c r="G142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H142">
+        <v>2755</v>
+      </c>
+      <c r="I142">
+        <v>1.347731</v>
+      </c>
+      <c r="J142">
+        <v>47.456310680000001</v>
+      </c>
+      <c r="K142">
+        <v>160</v>
+      </c>
+      <c r="L142" t="s">
+        <v>30</v>
+      </c>
+      <c r="M142">
+        <v>4888</v>
+      </c>
+      <c r="N142" t="s">
+        <v>63</v>
+      </c>
+      <c r="O142">
+        <v>3713</v>
+      </c>
+      <c r="P142">
+        <v>1316.455696</v>
+      </c>
+      <c r="Q142">
+        <v>103</v>
+      </c>
+      <c r="S142">
+        <v>47.456310999999999</v>
+      </c>
+      <c r="T142">
+        <v>2.7740369999999999</v>
+      </c>
+      <c r="U142">
+        <v>118</v>
+      </c>
+      <c r="V142">
+        <v>3.178023</v>
+      </c>
+      <c r="W142">
+        <v>41.423729000000002</v>
+      </c>
+      <c r="X142">
+        <v>82</v>
+      </c>
+      <c r="Y142">
+        <v>59.609755999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>25</v>
+      </c>
+      <c r="B143" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" t="s">
+        <v>216</v>
+      </c>
+      <c r="D143" t="s">
+        <v>38</v>
+      </c>
+      <c r="E143" t="s">
+        <v>29</v>
+      </c>
+      <c r="F143">
+        <v>71</v>
+      </c>
+      <c r="G143" t="s">
+        <v>39</v>
+      </c>
+      <c r="H143">
+        <v>2251</v>
+      </c>
+      <c r="I143">
+        <v>1.081297</v>
+      </c>
+      <c r="J143">
+        <v>69.084507040000005</v>
+      </c>
+      <c r="K143">
+        <v>160</v>
+      </c>
+      <c r="L143" t="s">
+        <v>30</v>
+      </c>
+      <c r="M143">
+        <v>4905</v>
+      </c>
+      <c r="N143" t="s">
+        <v>63</v>
+      </c>
+      <c r="O143">
+        <v>2434</v>
+      </c>
+      <c r="P143">
+        <v>2015.201315</v>
+      </c>
+      <c r="Q143">
+        <v>71</v>
+      </c>
+      <c r="S143">
+        <v>69.084507000000002</v>
+      </c>
+      <c r="T143">
+        <v>2.9170090000000002</v>
+      </c>
+      <c r="U143">
+        <v>72</v>
+      </c>
+      <c r="V143">
+        <v>2.958094</v>
+      </c>
+      <c r="W143">
+        <v>68.125</v>
+      </c>
+      <c r="X143">
+        <v>1</v>
+      </c>
+      <c r="Y143">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="B144" t="s">
+        <v>26</v>
+      </c>
+      <c r="C144" t="s">
+        <v>217</v>
+      </c>
+      <c r="D144" t="s">
+        <v>38</v>
+      </c>
+      <c r="E144" t="s">
+        <v>29</v>
+      </c>
+      <c r="F144">
+        <v>116</v>
+      </c>
+      <c r="G144" t="s">
+        <v>39</v>
+      </c>
+      <c r="H144">
+        <v>4310</v>
+      </c>
+      <c r="I144">
+        <v>1.5310900000000001</v>
+      </c>
+      <c r="J144">
+        <v>42.060344829999998</v>
+      </c>
+      <c r="K144">
+        <v>160</v>
+      </c>
+      <c r="L144" t="s">
+        <v>30</v>
+      </c>
+      <c r="M144">
+        <v>4879</v>
+      </c>
+      <c r="N144" t="s">
+        <v>63</v>
+      </c>
+      <c r="O144">
+        <v>6599</v>
+      </c>
+      <c r="P144">
+        <v>739.35444800000005</v>
+      </c>
+      <c r="Q144">
+        <v>116</v>
+      </c>
+      <c r="S144">
+        <v>42.060344999999998</v>
+      </c>
+      <c r="T144">
+        <v>1.7578419999999999</v>
+      </c>
+      <c r="U144">
+        <v>145</v>
+      </c>
+      <c r="V144">
+        <v>2.1973029999999998</v>
+      </c>
+      <c r="W144">
+        <v>33.648276000000003</v>
+      </c>
+      <c r="X144">
+        <v>98</v>
+      </c>
+      <c r="Y144">
+        <v>49.785713999999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145" t="s">
+        <v>26</v>
+      </c>
+      <c r="C145" t="s">
+        <v>218</v>
+      </c>
+      <c r="D145" t="s">
+        <v>38</v>
+      </c>
+      <c r="E145" t="s">
+        <v>29</v>
+      </c>
+      <c r="F145">
+        <v>133</v>
+      </c>
+      <c r="G145" t="s">
+        <v>39</v>
+      </c>
+      <c r="H145">
+        <v>3285</v>
+      </c>
+      <c r="I145">
+        <v>1.977473</v>
+      </c>
+      <c r="J145">
+        <v>36.714285709999999</v>
+      </c>
+      <c r="K145">
+        <v>160</v>
+      </c>
+      <c r="L145" t="s">
+        <v>30</v>
+      </c>
+      <c r="M145">
+        <v>4883</v>
+      </c>
+      <c r="N145" t="s">
+        <v>63</v>
+      </c>
+      <c r="O145">
+        <v>6496</v>
+      </c>
+      <c r="P145">
+        <v>751.69335000000001</v>
+      </c>
+      <c r="Q145">
+        <v>133</v>
+      </c>
+      <c r="S145">
+        <v>36.714286000000001</v>
+      </c>
+      <c r="T145">
+        <v>2.0474139999999998</v>
+      </c>
+      <c r="U145">
+        <v>212</v>
+      </c>
+      <c r="V145">
+        <v>3.263547</v>
+      </c>
+      <c r="W145">
+        <v>23.033018999999999</v>
+      </c>
+      <c r="X145">
+        <v>140</v>
+      </c>
+      <c r="Y145">
+        <v>34.878571000000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146" t="s">
+        <v>26</v>
+      </c>
+      <c r="C146" t="s">
+        <v>219</v>
+      </c>
+      <c r="D146" t="s">
+        <v>38</v>
+      </c>
+      <c r="E146" t="s">
+        <v>29</v>
+      </c>
+      <c r="F146">
+        <v>86</v>
+      </c>
+      <c r="G146" t="s">
+        <v>39</v>
+      </c>
+      <c r="H146">
+        <v>2687</v>
+      </c>
+      <c r="I146">
+        <v>1.2352069999999999</v>
+      </c>
+      <c r="J146">
+        <v>56.825581399999997</v>
+      </c>
+      <c r="K146">
+        <v>160</v>
+      </c>
+      <c r="L146" t="s">
+        <v>30</v>
+      </c>
+      <c r="M146">
+        <v>4887</v>
+      </c>
+      <c r="N146" t="s">
+        <v>63</v>
+      </c>
+      <c r="O146">
+        <v>3319</v>
+      </c>
+      <c r="P146">
+        <v>1472.4314549999999</v>
+      </c>
+      <c r="Q146">
+        <v>86</v>
+      </c>
+      <c r="S146">
+        <v>56.825581</v>
+      </c>
+      <c r="T146">
+        <v>2.5911420000000001</v>
+      </c>
+      <c r="U146">
+        <v>94</v>
+      </c>
+      <c r="V146">
+        <v>2.8321779999999999</v>
+      </c>
+      <c r="W146">
+        <v>51.989362</v>
+      </c>
+      <c r="X146">
+        <v>66</v>
+      </c>
+      <c r="Y146">
+        <v>74.045455000000004</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>25</v>
+      </c>
+      <c r="B147" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" t="s">
+        <v>220</v>
+      </c>
+      <c r="D147" t="s">
+        <v>38</v>
+      </c>
+      <c r="E147" t="s">
+        <v>29</v>
+      </c>
+      <c r="F147">
+        <v>137</v>
+      </c>
+      <c r="G147" t="s">
+        <v>39</v>
+      </c>
+      <c r="H147">
+        <v>3293</v>
+      </c>
+      <c r="I147">
+        <v>1.3209839999999999</v>
+      </c>
+      <c r="J147">
+        <v>35.496350360000001</v>
+      </c>
+      <c r="K147">
+        <v>160</v>
+      </c>
+      <c r="L147" t="s">
+        <v>30</v>
+      </c>
+      <c r="M147">
+        <v>4863</v>
+      </c>
+      <c r="N147" t="s">
+        <v>63</v>
+      </c>
+      <c r="O147">
+        <v>4350</v>
+      </c>
+      <c r="P147">
+        <v>1117.931034</v>
+      </c>
+      <c r="Q147">
+        <v>137</v>
+      </c>
+      <c r="S147">
+        <v>35.49635</v>
+      </c>
+      <c r="T147">
+        <v>3.1494249999999999</v>
+      </c>
+      <c r="U147">
+        <v>145</v>
+      </c>
+      <c r="V147">
+        <v>3.3333330000000001</v>
+      </c>
+      <c r="W147">
+        <v>33.537931</v>
+      </c>
+      <c r="X147">
+        <v>104</v>
+      </c>
+      <c r="Y147">
+        <v>46.759614999999997</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>25</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>221</v>
+      </c>
+      <c r="D148" t="s">
+        <v>28</v>
+      </c>
+      <c r="E148" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148">
+        <v>90</v>
+      </c>
+      <c r="G148" t="s">
+        <v>39</v>
+      </c>
+      <c r="H148">
+        <v>3629</v>
+      </c>
+      <c r="I148">
+        <v>1.263433</v>
+      </c>
+      <c r="J148">
+        <v>53.866666670000001</v>
+      </c>
+      <c r="K148">
+        <v>160</v>
+      </c>
+      <c r="L148" t="s">
+        <v>30</v>
+      </c>
+      <c r="M148">
+        <v>4848</v>
+      </c>
+      <c r="N148" t="s">
+        <v>63</v>
+      </c>
+      <c r="O148">
+        <v>4585</v>
+      </c>
+      <c r="P148">
+        <v>1057.36096</v>
+      </c>
+      <c r="Q148">
+        <v>90</v>
+      </c>
+      <c r="S148">
+        <v>53.866667</v>
+      </c>
+      <c r="T148">
+        <v>1.962923</v>
+      </c>
+      <c r="U148">
+        <v>110</v>
+      </c>
+      <c r="V148">
+        <v>2.3991280000000001</v>
+      </c>
+      <c r="W148">
+        <v>44.072727</v>
+      </c>
+      <c r="X148">
+        <v>63</v>
+      </c>
+      <c r="Y148">
+        <v>76.952381000000003</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>25</v>
+      </c>
+      <c r="B149" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" t="s">
+        <v>211</v>
+      </c>
+      <c r="D149" t="s">
+        <v>81</v>
+      </c>
+      <c r="E149" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149">
+        <v>101</v>
+      </c>
+      <c r="G149" t="s">
+        <v>39</v>
+      </c>
+      <c r="H149">
+        <v>2758</v>
+      </c>
+      <c r="I149">
+        <v>1.732777</v>
+      </c>
+      <c r="J149">
+        <v>67.564356439999997</v>
+      </c>
+      <c r="K149">
+        <v>320</v>
+      </c>
+      <c r="L149" t="s">
+        <v>30</v>
+      </c>
+      <c r="M149">
+        <v>6824</v>
+      </c>
+      <c r="N149" t="s">
+        <v>185</v>
+      </c>
+      <c r="O149">
+        <v>4779</v>
+      </c>
+      <c r="P149">
+        <v>1427.9137900000001</v>
+      </c>
+      <c r="Q149">
+        <v>101</v>
+      </c>
+      <c r="S149">
+        <v>67.564356000000004</v>
+      </c>
+      <c r="T149">
+        <v>2.113413</v>
+      </c>
+      <c r="U149">
+        <v>104</v>
+      </c>
+      <c r="V149">
+        <v>2.1761870000000001</v>
+      </c>
+      <c r="W149">
+        <v>65.615385000000003</v>
+      </c>
+      <c r="X149">
+        <v>73</v>
+      </c>
+      <c r="Y149">
+        <v>93.479451999999995</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>25</v>
+      </c>
+      <c r="B150" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D150" t="s">
+        <v>28</v>
+      </c>
+      <c r="E150" t="s">
+        <v>29</v>
+      </c>
+      <c r="F150">
+        <v>371</v>
+      </c>
+      <c r="G150" t="s">
+        <v>39</v>
+      </c>
+      <c r="H150">
+        <v>19253</v>
+      </c>
+      <c r="I150">
+        <v>1.0852850000000001</v>
+      </c>
+      <c r="J150">
+        <v>121.03504043</v>
+      </c>
+      <c r="K150">
+        <v>58000</v>
+      </c>
+      <c r="L150" t="s">
+        <v>30</v>
+      </c>
+      <c r="M150">
+        <v>44904</v>
+      </c>
+      <c r="N150" t="s">
+        <v>222</v>
+      </c>
+      <c r="O150">
+        <v>20895</v>
+      </c>
+      <c r="P150">
+        <v>2149.0308690000002</v>
+      </c>
+      <c r="Q150">
+        <v>371</v>
+      </c>
+      <c r="S150">
+        <v>121.03504</v>
+      </c>
+      <c r="T150">
+        <v>1.775544</v>
+      </c>
+      <c r="U150">
+        <v>394</v>
+      </c>
+      <c r="V150">
+        <v>1.8856189999999999</v>
+      </c>
+      <c r="W150">
+        <v>113.969543</v>
+      </c>
+      <c r="X150">
+        <v>278</v>
+      </c>
+      <c r="Y150">
+        <v>161.52518000000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" t="s">
+        <v>223</v>
+      </c>
+      <c r="D151" t="s">
+        <v>38</v>
+      </c>
+      <c r="E151" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151">
+        <v>12</v>
+      </c>
+      <c r="G151" t="s">
+        <v>39</v>
+      </c>
+      <c r="H151">
+        <v>525</v>
+      </c>
+      <c r="I151">
+        <v>1.1257140000000001</v>
+      </c>
+      <c r="J151">
+        <v>33.833333330000002</v>
+      </c>
+      <c r="K151">
+        <v>160</v>
+      </c>
+      <c r="L151" t="s">
+        <v>30</v>
+      </c>
+      <c r="M151">
+        <v>406</v>
+      </c>
+      <c r="N151" t="s">
+        <v>224</v>
+      </c>
+      <c r="O151">
+        <v>591</v>
+      </c>
+      <c r="P151">
+        <v>686.97123499999998</v>
+      </c>
+      <c r="Q151">
+        <v>12</v>
+      </c>
+      <c r="S151">
+        <v>33.833333000000003</v>
+      </c>
+      <c r="T151">
+        <v>2.0304570000000002</v>
+      </c>
+      <c r="U151">
+        <v>18</v>
+      </c>
+      <c r="V151">
+        <v>3.0456850000000002</v>
+      </c>
+      <c r="W151">
+        <v>22.555555999999999</v>
+      </c>
+      <c r="X151">
+        <v>13</v>
+      </c>
+      <c r="Y151">
+        <v>31.230768999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>25</v>
+      </c>
+      <c r="B152" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" t="s">
+        <v>225</v>
+      </c>
+      <c r="D152" t="s">
+        <v>38</v>
+      </c>
+      <c r="E152" t="s">
+        <v>29</v>
+      </c>
+      <c r="F152">
+        <v>14</v>
+      </c>
+      <c r="G152" t="s">
+        <v>39</v>
+      </c>
+      <c r="H152">
+        <v>492</v>
+      </c>
+      <c r="I152">
+        <v>1.2337400000000001</v>
+      </c>
+      <c r="J152">
+        <v>26.85714286</v>
+      </c>
+      <c r="K152">
+        <v>160</v>
+      </c>
+      <c r="L152" t="s">
+        <v>30</v>
+      </c>
+      <c r="M152">
+        <v>376</v>
+      </c>
+      <c r="N152" t="s">
+        <v>224</v>
+      </c>
+      <c r="O152">
+        <v>607</v>
+      </c>
+      <c r="P152">
+        <v>619.43986800000005</v>
+      </c>
+      <c r="Q152">
+        <v>14</v>
+      </c>
+      <c r="S152">
+        <v>26.857143000000001</v>
+      </c>
+      <c r="T152">
+        <v>2.3064249999999999</v>
+      </c>
+      <c r="U152">
+        <v>18</v>
+      </c>
+      <c r="V152">
+        <v>2.9654039999999999</v>
+      </c>
+      <c r="W152">
+        <v>20.888888999999999</v>
+      </c>
+      <c r="X152">
+        <v>1</v>
+      </c>
+      <c r="Y152">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>25</v>
+      </c>
+      <c r="B153" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153" t="s">
+        <v>226</v>
+      </c>
+      <c r="D153" t="s">
+        <v>38</v>
+      </c>
+      <c r="E153" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153">
+        <v>19</v>
+      </c>
+      <c r="G153" t="s">
+        <v>39</v>
+      </c>
+      <c r="H153">
+        <v>367</v>
+      </c>
+      <c r="I153">
+        <v>1.1880109999999999</v>
+      </c>
+      <c r="J153">
+        <v>20.526315790000002</v>
+      </c>
+      <c r="K153">
+        <v>160</v>
+      </c>
+      <c r="L153" t="s">
+        <v>30</v>
+      </c>
+      <c r="M153">
+        <v>390</v>
+      </c>
+      <c r="N153" t="s">
+        <v>224</v>
+      </c>
+      <c r="O153">
+        <v>436</v>
+      </c>
+      <c r="P153">
+        <v>894.49541299999999</v>
+      </c>
+      <c r="Q153">
+        <v>19</v>
+      </c>
+      <c r="S153">
+        <v>20.526316000000001</v>
+      </c>
+      <c r="T153">
+        <v>4.3577979999999998</v>
+      </c>
+      <c r="U153">
+        <v>21</v>
+      </c>
+      <c r="V153">
+        <v>4.8165139999999997</v>
+      </c>
+      <c r="W153">
+        <v>18.571428999999998</v>
+      </c>
+      <c r="X153">
+        <v>18</v>
+      </c>
+      <c r="Y153">
+        <v>21.666667</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>25</v>
+      </c>
+      <c r="B154" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" t="s">
+        <v>227</v>
+      </c>
+      <c r="D154" t="s">
+        <v>38</v>
+      </c>
+      <c r="E154" t="s">
+        <v>29</v>
+      </c>
+      <c r="F154">
+        <v>31</v>
+      </c>
+      <c r="G154" t="s">
+        <v>39</v>
+      </c>
+      <c r="H154">
+        <v>551</v>
+      </c>
+      <c r="I154">
+        <v>1.116152</v>
+      </c>
+      <c r="J154">
+        <v>13</v>
+      </c>
+      <c r="K154">
+        <v>160</v>
+      </c>
+      <c r="L154" t="s">
+        <v>30</v>
+      </c>
+      <c r="M154">
+        <v>403</v>
+      </c>
+      <c r="N154" t="s">
+        <v>224</v>
+      </c>
+      <c r="O154">
+        <v>615</v>
+      </c>
+      <c r="P154">
+        <v>655.28455299999996</v>
+      </c>
+      <c r="Q154">
+        <v>31</v>
+      </c>
+      <c r="S154">
+        <v>13</v>
+      </c>
+      <c r="T154">
+        <v>5.0406500000000003</v>
+      </c>
+      <c r="U154">
+        <v>38</v>
+      </c>
+      <c r="V154">
+        <v>6.1788619999999996</v>
+      </c>
+      <c r="W154">
+        <v>10.605263000000001</v>
+      </c>
+      <c r="X154">
+        <v>30</v>
+      </c>
+      <c r="Y154">
+        <v>13.433332999999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>25</v>
+      </c>
+      <c r="B155" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" t="s">
+        <v>228</v>
+      </c>
+      <c r="D155" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" t="s">
+        <v>29</v>
+      </c>
+      <c r="F155">
+        <v>5</v>
+      </c>
+      <c r="G155" t="s">
+        <v>39</v>
+      </c>
+      <c r="H155">
+        <v>320</v>
+      </c>
+      <c r="I155">
+        <v>1.3218749999999999</v>
+      </c>
+      <c r="J155">
+        <v>85.8</v>
+      </c>
+      <c r="K155">
+        <v>160</v>
+      </c>
+      <c r="L155" t="s">
+        <v>30</v>
+      </c>
+      <c r="M155">
+        <v>429</v>
+      </c>
+      <c r="N155" t="s">
+        <v>224</v>
+      </c>
+      <c r="O155">
+        <v>423</v>
+      </c>
+      <c r="P155">
+        <v>1014.184397</v>
+      </c>
+      <c r="Q155">
+        <v>5</v>
+      </c>
+      <c r="S155">
+        <v>85.8</v>
+      </c>
+      <c r="T155">
+        <v>1.1820329999999999</v>
+      </c>
+      <c r="U155">
+        <v>4</v>
+      </c>
+      <c r="V155">
+        <v>0.94562599999999997</v>
+      </c>
+      <c r="W155">
+        <v>107.25</v>
+      </c>
+      <c r="X155">
+        <v>2</v>
+      </c>
+      <c r="Y155">
+        <v>214.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>25</v>
+      </c>
+      <c r="B156" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" t="s">
+        <v>229</v>
+      </c>
+      <c r="D156" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" t="s">
+        <v>29</v>
+      </c>
+      <c r="F156">
+        <v>28</v>
+      </c>
+      <c r="G156" t="s">
+        <v>39</v>
+      </c>
+      <c r="H156">
+        <v>474</v>
+      </c>
+      <c r="I156">
+        <v>1.1244730000000001</v>
+      </c>
+      <c r="J156">
+        <v>13.89285714</v>
+      </c>
+      <c r="K156">
+        <v>160</v>
+      </c>
+      <c r="L156" t="s">
+        <v>30</v>
+      </c>
+      <c r="M156">
+        <v>389</v>
+      </c>
+      <c r="N156" t="s">
+        <v>224</v>
+      </c>
+      <c r="O156">
+        <v>533</v>
+      </c>
+      <c r="P156">
+        <v>729.83114399999999</v>
+      </c>
+      <c r="Q156">
+        <v>28</v>
+      </c>
+      <c r="S156">
+        <v>13.892856999999999</v>
+      </c>
+      <c r="T156">
+        <v>5.2532829999999997</v>
+      </c>
+      <c r="U156">
+        <v>32</v>
+      </c>
+      <c r="V156">
+        <v>6.0037520000000004</v>
+      </c>
+      <c r="W156">
+        <v>12.15625</v>
+      </c>
+      <c r="X156">
+        <v>1</v>
+      </c>
+      <c r="Y156">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>25</v>
+      </c>
+      <c r="B157" t="s">
+        <v>26</v>
+      </c>
+      <c r="C157" t="s">
+        <v>230</v>
+      </c>
+      <c r="D157" t="s">
+        <v>38</v>
+      </c>
+      <c r="E157" t="s">
+        <v>29</v>
+      </c>
+      <c r="F157">
+        <v>24</v>
+      </c>
+      <c r="G157" t="s">
+        <v>39</v>
+      </c>
+      <c r="H157">
+        <v>352</v>
+      </c>
+      <c r="I157">
+        <v>1.193182</v>
+      </c>
+      <c r="J157">
+        <v>16.708333329999999</v>
+      </c>
+      <c r="K157">
+        <v>160</v>
+      </c>
+      <c r="L157" t="s">
+        <v>30</v>
+      </c>
+      <c r="M157">
+        <v>401</v>
+      </c>
+      <c r="N157" t="s">
+        <v>224</v>
+      </c>
+      <c r="O157">
+        <v>420</v>
+      </c>
+      <c r="P157">
+        <v>954.76190499999996</v>
+      </c>
+      <c r="Q157">
+        <v>24</v>
+      </c>
+      <c r="S157">
+        <v>16.708333</v>
+      </c>
+      <c r="T157">
+        <v>5.7142860000000004</v>
+      </c>
+      <c r="U157">
+        <v>33</v>
+      </c>
+      <c r="V157">
+        <v>7.8571429999999998</v>
+      </c>
+      <c r="W157">
+        <v>12.151515</v>
+      </c>
+      <c r="X157">
+        <v>22</v>
+      </c>
+      <c r="Y157">
+        <v>18.227273</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>25</v>
+      </c>
+      <c r="B158" t="s">
+        <v>26</v>
+      </c>
+      <c r="C158" t="s">
+        <v>231</v>
+      </c>
+      <c r="D158" t="s">
+        <v>28</v>
+      </c>
+      <c r="E158" t="s">
+        <v>29</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>160</v>
+      </c>
+      <c r="L158" t="s">
+        <v>30</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158" t="s">
+        <v>154</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>0</v>
+      </c>
+      <c r="U158">
+        <v>0</v>
+      </c>
+      <c r="V158">
+        <v>0</v>
+      </c>
+      <c r="W158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>25</v>
+      </c>
+      <c r="B159" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159" t="s">
+        <v>153</v>
+      </c>
+      <c r="D159" t="s">
+        <v>28</v>
+      </c>
+      <c r="E159" t="s">
+        <v>29</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>160</v>
+      </c>
+      <c r="L159" t="s">
+        <v>30</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159" t="s">
+        <v>154</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>0</v>
+      </c>
+      <c r="U159">
+        <v>0</v>
+      </c>
+      <c r="V159">
+        <v>0</v>
+      </c>
+      <c r="W159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>25</v>
+      </c>
+      <c r="B160" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" t="s">
+        <v>232</v>
+      </c>
+      <c r="D160" t="s">
+        <v>28</v>
+      </c>
+      <c r="E160" t="s">
+        <v>29</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>160</v>
+      </c>
+      <c r="L160" t="s">
+        <v>30</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160" t="s">
+        <v>233</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>0</v>
+      </c>
+      <c r="U160">
+        <v>0</v>
+      </c>
+      <c r="V160">
+        <v>0</v>
+      </c>
+      <c r="W160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>25</v>
+      </c>
+      <c r="B161" t="s">
+        <v>26</v>
+      </c>
+      <c r="C161" t="s">
+        <v>234</v>
+      </c>
+      <c r="D161" t="s">
+        <v>28</v>
+      </c>
+      <c r="E161" t="s">
+        <v>29</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>160</v>
+      </c>
+      <c r="L161" t="s">
+        <v>30</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161" t="s">
+        <v>112</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>0</v>
+      </c>
+      <c r="U161">
+        <v>0</v>
+      </c>
+      <c r="V161">
+        <v>0</v>
+      </c>
+      <c r="W161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>25</v>
+      </c>
+      <c r="B162" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" t="s">
+        <v>235</v>
+      </c>
+      <c r="D162" t="s">
+        <v>28</v>
+      </c>
+      <c r="E162" t="s">
+        <v>29</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>160</v>
+      </c>
+      <c r="L162" t="s">
+        <v>30</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162" t="s">
+        <v>112</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>0</v>
+      </c>
+      <c r="U162">
+        <v>0</v>
+      </c>
+      <c r="V162">
+        <v>0</v>
+      </c>
+      <c r="W162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>25</v>
+      </c>
+      <c r="B163" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" t="s">
+        <v>236</v>
+      </c>
+      <c r="D163" t="s">
+        <v>28</v>
+      </c>
+      <c r="E163" t="s">
+        <v>29</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>320</v>
+      </c>
+      <c r="L163" t="s">
+        <v>30</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163" t="s">
+        <v>112</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="U163">
+        <v>0</v>
+      </c>
+      <c r="V163">
+        <v>0</v>
+      </c>
+      <c r="W163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>25</v>
+      </c>
+      <c r="B164" t="s">
+        <v>26</v>
+      </c>
+      <c r="C164" t="s">
+        <v>237</v>
+      </c>
+      <c r="D164" t="s">
+        <v>28</v>
+      </c>
+      <c r="E164" t="s">
+        <v>29</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>160</v>
+      </c>
+      <c r="L164" t="s">
+        <v>30</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164" t="s">
+        <v>112</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="U164">
+        <v>0</v>
+      </c>
+      <c r="V164">
+        <v>0</v>
+      </c>
+      <c r="W164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>25</v>
+      </c>
+      <c r="B165" t="s">
+        <v>26</v>
+      </c>
+      <c r="C165" t="s">
+        <v>238</v>
+      </c>
+      <c r="D165" t="s">
+        <v>28</v>
+      </c>
+      <c r="E165" t="s">
+        <v>29</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>160</v>
+      </c>
+      <c r="L165" t="s">
+        <v>30</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165" t="s">
+        <v>112</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="U165">
+        <v>0</v>
+      </c>
+      <c r="V165">
+        <v>0</v>
+      </c>
+      <c r="W165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166" t="s">
+        <v>26</v>
+      </c>
+      <c r="C166" t="s">
+        <v>231</v>
+      </c>
+      <c r="D166" t="s">
+        <v>28</v>
+      </c>
+      <c r="E166" t="s">
+        <v>29</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>160</v>
+      </c>
+      <c r="L166" t="s">
+        <v>30</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166" t="s">
+        <v>154</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="U166">
+        <v>0</v>
+      </c>
+      <c r="V166">
+        <v>0</v>
+      </c>
+      <c r="W166">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
